--- a/plots-eff1-new-both/particle_both_motion_data.xlsx
+++ b/plots-eff1-new-both/particle_both_motion_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Detailed_Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary_Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/plots-eff1-new-both/particle_both_motion_data.xlsx
+++ b/plots-eff1-new-both/particle_both_motion_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed_Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Detailed_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary_Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,12 +442,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Height_cm</t>
+          <t>Height_mm</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Inner_Diameter_cm</t>
+          <t>Inner_Diameter_mm</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -497,12 +497,12 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Inner_Radius_cm</t>
+          <t>Inner_Radius_mm</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Revolution_Radius_cm</t>
+          <t>Revolution_Radius_mm</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.445578231292517</v>
+        <v>4.45578231292517</v>
       </c>
       <c r="D2" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E2" t="n">
         <v>1018.897297297297</v>
@@ -561,10 +561,10 @@
         <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O2" t="n">
-        <v>1.130396713140702</v>
+        <v>11.30396713140702</v>
       </c>
       <c r="P2" t="n">
         <v>0.8838740257004424</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.897959183673469</v>
+        <v>18.97959183673469</v>
       </c>
       <c r="D3" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E3" t="n">
         <v>1478.4</v>
@@ -618,10 +618,10 @@
         <v>12.5</v>
       </c>
       <c r="N3" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O3" t="n">
-        <v>1.155149188388227</v>
+        <v>11.55149188388227</v>
       </c>
       <c r="P3" t="n">
         <v>0.9032283547503687</v>
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.244897959183673</v>
+        <v>32.44897959183673</v>
       </c>
       <c r="D4" t="n">
-        <v>2.524694809430622</v>
+        <v>25.24694809430622</v>
       </c>
       <c r="E4" t="n">
         <v>1018.897297297297</v>
@@ -675,10 +675,10 @@
         <v>10.73225806451615</v>
       </c>
       <c r="N4" t="n">
-        <v>1.262347404715311</v>
+        <v>12.62347404715311</v>
       </c>
       <c r="O4" t="n">
-        <v>1.156087423878517</v>
+        <v>11.56087423878517</v>
       </c>
       <c r="P4" t="n">
         <v>0.9158235043381282</v>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.040816326530612</v>
+        <v>40.40816326530611</v>
       </c>
       <c r="D5" t="n">
-        <v>2.441244991147143</v>
+        <v>24.41244991147143</v>
       </c>
       <c r="E5" t="n">
         <v>1108.8</v>
@@ -732,10 +732,10 @@
         <v>10.73709677419356</v>
       </c>
       <c r="N5" t="n">
-        <v>1.220622495573572</v>
+        <v>12.20622495573572</v>
       </c>
       <c r="O5" t="n">
-        <v>1.11431460672017</v>
+        <v>11.1431460672017</v>
       </c>
       <c r="P5" t="n">
         <v>0.9129068248054469</v>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3979591836734694</v>
+        <v>3.979591836734694</v>
       </c>
       <c r="D6" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E6" t="n">
         <v>1346.4</v>
@@ -789,10 +789,10 @@
         <v>36</v>
       </c>
       <c r="N6" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9224759210614939</v>
+        <v>9.224759210614939</v>
       </c>
       <c r="P6" t="n">
         <v>0.7212976616810618</v>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.08843537414966</v>
+        <v>50.8843537414966</v>
       </c>
       <c r="D7" t="n">
-        <v>2.309989749324387</v>
+        <v>23.09989749324387</v>
       </c>
       <c r="E7" t="n">
         <v>966.6461538461538</v>
@@ -846,10 +846,10 @@
         <v>10.1483870967742</v>
       </c>
       <c r="N7" t="n">
-        <v>1.154994874662194</v>
+        <v>11.54994874662194</v>
       </c>
       <c r="O7" t="n">
-        <v>1.054515794496113</v>
+        <v>10.54515794496113</v>
       </c>
       <c r="P7" t="n">
         <v>0.9130047393539571</v>
@@ -870,10 +870,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4863945578231292</v>
+        <v>4.863945578231292</v>
       </c>
       <c r="D8" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E8" t="n">
         <v>1396.266666666667</v>
@@ -903,10 +903,10 @@
         <v>21.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O8" t="n">
-        <v>1.066040277497138</v>
+        <v>10.66040277497138</v>
       </c>
       <c r="P8" t="n">
         <v>0.8335527701706341</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.5</v>
+        <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>2.389455782312925</v>
+        <v>23.89455782312925</v>
       </c>
       <c r="E9" t="n">
         <v>1069.48085106383</v>
@@ -960,10 +960,10 @@
         <v>13.00967741935483</v>
       </c>
       <c r="N9" t="n">
-        <v>1.194727891156462</v>
+        <v>11.94727891156463</v>
       </c>
       <c r="O9" t="n">
-        <v>1.065919203836118</v>
+        <v>10.65919203836118</v>
       </c>
       <c r="P9" t="n">
         <v>0.8921857535311563</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.979591836734694</v>
+        <v>19.79591836734694</v>
       </c>
       <c r="D10" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E10" t="n">
         <v>1185.509433962264</v>
@@ -1017,10 +1017,10 @@
         <v>11.5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O10" t="n">
-        <v>1.165050178487236</v>
+        <v>11.65050178487236</v>
       </c>
       <c r="P10" t="n">
         <v>0.9109700863703392</v>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8367346938775511</v>
+        <v>8.36734693877551</v>
       </c>
       <c r="D11" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E11" t="n">
         <v>1346.4</v>
@@ -1074,10 +1074,10 @@
         <v>15</v>
       </c>
       <c r="N11" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O11" t="n">
-        <v>1.130396713140702</v>
+        <v>11.30396713140702</v>
       </c>
       <c r="P11" t="n">
         <v>0.8838740257004424</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.061224489795919</v>
+        <v>40.61224489795919</v>
       </c>
       <c r="D12" t="n">
-        <v>2.436212841300904</v>
+        <v>24.36212841300904</v>
       </c>
       <c r="E12" t="n">
         <v>661.3894736842104</v>
@@ -1131,10 +1131,10 @@
         <v>15.70645161290321</v>
       </c>
       <c r="N12" t="n">
-        <v>1.218106420650452</v>
+        <v>12.18106420650452</v>
       </c>
       <c r="O12" t="n">
-        <v>1.062596998740519</v>
+        <v>10.62596998740519</v>
       </c>
       <c r="P12" t="n">
         <v>0.8723351102386498</v>
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.370748299319728</v>
+        <v>23.70748299319728</v>
       </c>
       <c r="D13" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E13" t="n">
         <v>819.5478260869564</v>
@@ -1188,10 +1188,10 @@
         <v>11.5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O13" t="n">
-        <v>1.165050178487236</v>
+        <v>11.65050178487236</v>
       </c>
       <c r="P13" t="n">
         <v>0.9109700863703392</v>
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.673469387755102</v>
+        <v>16.73469387755102</v>
       </c>
       <c r="D14" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E14" t="n">
         <v>1142.4</v>
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="N14" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O14" t="n">
-        <v>1.170000673536741</v>
+        <v>11.70000673536741</v>
       </c>
       <c r="P14" t="n">
         <v>0.9148409521803245</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9761904761904762</v>
+        <v>9.761904761904761</v>
       </c>
       <c r="D15" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E15" t="n">
         <v>1216.103225806452</v>
@@ -1302,10 +1302,10 @@
         <v>12</v>
       </c>
       <c r="N15" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O15" t="n">
-        <v>1.160099683437732</v>
+        <v>11.60099683437732</v>
       </c>
       <c r="P15" t="n">
         <v>0.907099220560354</v>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.204081632653061</v>
+        <v>52.04081632653061</v>
       </c>
       <c r="D16" t="n">
-        <v>2.299506103811388</v>
+        <v>22.99506103811388</v>
       </c>
       <c r="E16" t="n">
         <v>739.1999999999999</v>
@@ -1359,10 +1359,10 @@
         <v>17.87258064516129</v>
       </c>
       <c r="N16" t="n">
-        <v>1.149753051905694</v>
+        <v>11.49753051905694</v>
       </c>
       <c r="O16" t="n">
-        <v>0.972796807894196</v>
+        <v>9.727968078941959</v>
       </c>
       <c r="P16" t="n">
         <v>0.8460919553827699</v>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.843537414965986</v>
+        <v>18.43537414965986</v>
       </c>
       <c r="D17" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E17" t="n">
         <v>769.3714285714285</v>
@@ -1416,10 +1416,10 @@
         <v>13.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O17" t="n">
-        <v>1.145248198289217</v>
+        <v>11.45248198289217</v>
       </c>
       <c r="P17" t="n">
         <v>0.8954866231303982</v>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.224489795918367</v>
+        <v>72.24489795918367</v>
       </c>
       <c r="D18" t="n">
-        <v>2.028628395530592</v>
+        <v>20.28628395530592</v>
       </c>
       <c r="E18" t="n">
         <v>819.5478260869564</v>
@@ -1473,10 +1473,10 @@
         <v>8.801251956181545</v>
       </c>
       <c r="N18" t="n">
-        <v>1.014314197765296</v>
+        <v>10.14314197765296</v>
       </c>
       <c r="O18" t="n">
-        <v>0.927173089288251</v>
+        <v>9.271730892882511</v>
       </c>
       <c r="P18" t="n">
         <v>0.9140886436677792</v>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.642857142857142</v>
+        <v>86.42857142857142</v>
       </c>
       <c r="D19" t="n">
-        <v>1.867261988046933</v>
+        <v>18.67261988046933</v>
       </c>
       <c r="E19" t="n">
         <v>1277.938983050847</v>
@@ -1530,10 +1530,10 @@
         <v>8.266823161189365</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9336309940234664</v>
+        <v>9.336309940234663</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8517812597542649</v>
+        <v>8.517812597542649</v>
       </c>
       <c r="P19" t="n">
         <v>0.9123318154676169</v>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.340136054421768</v>
+        <v>93.40136054421768</v>
       </c>
       <c r="D20" t="n">
-        <v>1.794179375961942</v>
+        <v>17.94179375961942</v>
       </c>
       <c r="E20" t="n">
         <v>1288.861538461538</v>
@@ -1587,10 +1587,10 @@
         <v>9.967918622848202</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8970896879809709</v>
+        <v>8.970896879809709</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7983974243884144</v>
+        <v>7.983974243884145</v>
       </c>
       <c r="P20" t="n">
         <v>0.889986179849333</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.908163265306122</v>
+        <v>39.08163265306123</v>
       </c>
       <c r="D21" t="n">
-        <v>2.447744851365204</v>
+        <v>24.47744851365204</v>
       </c>
       <c r="E21" t="n">
         <v>1159.975384615384</v>
@@ -1644,10 +1644,10 @@
         <v>11.47258064516132</v>
       </c>
       <c r="N21" t="n">
-        <v>1.223872425682602</v>
+        <v>12.23872425682602</v>
       </c>
       <c r="O21" t="n">
-        <v>1.110282518304767</v>
+        <v>11.10282518304767</v>
       </c>
       <c r="P21" t="n">
         <v>0.9071881145500266</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.965986394557823</v>
+        <v>19.65986394557823</v>
       </c>
       <c r="D22" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E22" t="n">
         <v>1461.209302325581</v>
@@ -1701,10 +1701,10 @@
         <v>20.5</v>
       </c>
       <c r="N22" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O22" t="n">
-        <v>1.075941267596147</v>
+        <v>10.75941267596147</v>
       </c>
       <c r="P22" t="n">
         <v>0.8412945017906046</v>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.829931972789116</v>
+        <v>28.29931972789116</v>
       </c>
       <c r="D23" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E23" t="n">
         <v>919.4926829268292</v>
@@ -1758,10 +1758,10 @@
         <v>18</v>
       </c>
       <c r="N23" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O23" t="n">
-        <v>1.100693742843672</v>
+        <v>11.00693742843672</v>
       </c>
       <c r="P23" t="n">
         <v>0.8606488308405309</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5.023809523809524</v>
+        <v>50.23809523809524</v>
       </c>
       <c r="D24" t="n">
-        <v>2.314602553350107</v>
+        <v>23.14602553350107</v>
       </c>
       <c r="E24" t="n">
         <v>924</v>
@@ -1815,10 +1815,10 @@
         <v>23.83387096774192</v>
       </c>
       <c r="N24" t="n">
-        <v>1.157301276675054</v>
+        <v>11.57301276675054</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9213223562023616</v>
+        <v>9.213223562023616</v>
       </c>
       <c r="P24" t="n">
         <v>0.7960955152916934</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.040816326530612</v>
+        <v>40.40816326530611</v>
       </c>
       <c r="D25" t="n">
-        <v>2.430341999813624</v>
+        <v>24.30341999813624</v>
       </c>
       <c r="E25" t="n">
         <v>1282.285714285714</v>
@@ -1872,10 +1872,10 @@
         <v>17.71774193548384</v>
       </c>
       <c r="N25" t="n">
-        <v>1.215170999906812</v>
+        <v>12.15170999906812</v>
       </c>
       <c r="O25" t="n">
-        <v>1.039747812426774</v>
+        <v>10.39747812426774</v>
       </c>
       <c r="P25" t="n">
         <v>0.855639093186481</v>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.948979591836735</v>
+        <v>69.48979591836735</v>
       </c>
       <c r="D26" t="n">
-        <v>2.054743248915629</v>
+        <v>20.54743248915629</v>
       </c>
       <c r="E26" t="n">
         <v>966.6461538461538</v>
@@ -1929,10 +1929,10 @@
         <v>10.99921752738655</v>
       </c>
       <c r="N26" t="n">
-        <v>1.027371624457814</v>
+        <v>10.27371624457814</v>
       </c>
       <c r="O26" t="n">
-        <v>0.918468480622304</v>
+        <v>9.184684806223039</v>
       </c>
       <c r="P26" t="n">
         <v>0.8939982950249545</v>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.074829931972788</v>
+        <v>80.74829931972788</v>
       </c>
       <c r="D27" t="n">
-        <v>1.925922964680485</v>
+        <v>19.25922964680485</v>
       </c>
       <c r="E27" t="n">
         <v>919.4926829268292</v>
@@ -1986,10 +1986,10 @@
         <v>7.838028169014081</v>
       </c>
       <c r="N27" t="n">
-        <v>0.9629614823402426</v>
+        <v>9.629614823402425</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8853572430430735</v>
+        <v>8.853572430430734</v>
       </c>
       <c r="P27" t="n">
         <v>0.9194108583568983</v>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6.438775510204081</v>
+        <v>64.38775510204081</v>
       </c>
       <c r="D28" t="n">
-        <v>2.116717303963701</v>
+        <v>21.16717303963701</v>
       </c>
       <c r="E28" t="n">
         <v>1256.64</v>
@@ -2043,10 +2043,10 @@
         <v>13.32785602503913</v>
       </c>
       <c r="N28" t="n">
-        <v>1.05835865198185</v>
+        <v>10.5835865198185</v>
       </c>
       <c r="O28" t="n">
-        <v>0.9263996814369087</v>
+        <v>9.263996814369087</v>
       </c>
       <c r="P28" t="n">
         <v>0.8753173413399706</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.836734693877552</v>
+        <v>68.36734693877551</v>
       </c>
       <c r="D29" t="n">
-        <v>2.093330868096504</v>
+        <v>20.93330868096504</v>
       </c>
       <c r="E29" t="n">
         <v>897.5999999999999</v>
@@ -2100,10 +2100,10 @@
         <v>8.838810641627532</v>
       </c>
       <c r="N29" t="n">
-        <v>1.046665434048252</v>
+        <v>10.46665434048252</v>
       </c>
       <c r="O29" t="n">
-        <v>0.9591524573984743</v>
+        <v>9.591524573984744</v>
       </c>
       <c r="P29" t="n">
         <v>0.9163887773466463</v>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.948979591836735</v>
+        <v>79.48979591836735</v>
       </c>
       <c r="D30" t="n">
-        <v>1.939954826200803</v>
+        <v>19.39954826200803</v>
       </c>
       <c r="E30" t="n">
         <v>919.4926829268292</v>
@@ -2157,10 +2157,10 @@
         <v>11.64788732394365</v>
       </c>
       <c r="N30" t="n">
-        <v>0.9699774131004016</v>
+        <v>9.699774131004016</v>
       </c>
       <c r="O30" t="n">
-        <v>0.8546517960316526</v>
+        <v>8.546517960316526</v>
       </c>
       <c r="P30" t="n">
         <v>0.8811048427404858</v>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10.13605442176871</v>
+        <v>101.3605442176871</v>
       </c>
       <c r="D31" t="n">
-        <v>1.707844450218873</v>
+        <v>17.07844450218873</v>
       </c>
       <c r="E31" t="n">
         <v>1288.861538461538</v>
@@ -2214,10 +2214,10 @@
         <v>12.04773082942097</v>
       </c>
       <c r="N31" t="n">
-        <v>0.8539222251094365</v>
+        <v>8.539222251094365</v>
       </c>
       <c r="O31" t="n">
-        <v>0.7346377614518032</v>
+        <v>7.346377614518032</v>
       </c>
       <c r="P31" t="n">
         <v>0.8603099203298683</v>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7.884353741496599</v>
+        <v>78.84353741496599</v>
       </c>
       <c r="D32" t="n">
-        <v>1.954961122548921</v>
+        <v>19.54961122548922</v>
       </c>
       <c r="E32" t="n">
         <v>1648.052459016393</v>
@@ -2271,10 +2271,10 @@
         <v>14.7300469483568</v>
       </c>
       <c r="N32" t="n">
-        <v>0.9774805612744607</v>
+        <v>9.774805612744608</v>
       </c>
       <c r="O32" t="n">
-        <v>0.831638512280829</v>
+        <v>8.31638512280829</v>
       </c>
       <c r="P32" t="n">
         <v>0.8507980058411805</v>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8.687074829931973</v>
+        <v>86.87074829931973</v>
       </c>
       <c r="D33" t="n">
-        <v>1.862584700873493</v>
+        <v>18.62584700873493</v>
       </c>
       <c r="E33" t="n">
         <v>837.76</v>
@@ -2328,10 +2328,10 @@
         <v>13.05790297339593</v>
       </c>
       <c r="N33" t="n">
-        <v>0.9312923504367465</v>
+        <v>9.312923504367465</v>
       </c>
       <c r="O33" t="n">
-        <v>0.8020061823833216</v>
+        <v>8.020061823833215</v>
       </c>
       <c r="P33" t="n">
         <v>0.8611755288306686</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6.08843537414966</v>
+        <v>60.8843537414966</v>
       </c>
       <c r="D34" t="n">
-        <v>2.141467948589817</v>
+        <v>21.41467948589817</v>
       </c>
       <c r="E34" t="n">
         <v>1599.36</v>
@@ -2385,10 +2385,10 @@
         <v>15.88967136150234</v>
       </c>
       <c r="N34" t="n">
-        <v>1.070733974294909</v>
+        <v>10.70733974294909</v>
       </c>
       <c r="O34" t="n">
-        <v>0.9134104954681528</v>
+        <v>9.134104954681527</v>
       </c>
       <c r="P34" t="n">
         <v>0.8530694994241167</v>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6.122448979591836</v>
+        <v>61.22448979591837</v>
       </c>
       <c r="D35" t="n">
-        <v>2.140688400727578</v>
+        <v>21.40688400727578</v>
       </c>
       <c r="E35" t="n">
         <v>824.0262295081967</v>
@@ -2442,10 +2442,10 @@
         <v>11.52582159624413</v>
       </c>
       <c r="N35" t="n">
-        <v>1.070344200363789</v>
+        <v>10.70344200363789</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9562271548564213</v>
+        <v>9.562271548564214</v>
       </c>
       <c r="P35" t="n">
         <v>0.8933828524799953</v>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6.758503401360545</v>
+        <v>67.58503401360545</v>
       </c>
       <c r="D36" t="n">
-        <v>2.081832537128466</v>
+        <v>20.81832537128466</v>
       </c>
       <c r="E36" t="n">
         <v>1142.4</v>
@@ -2499,10 +2499,10 @@
         <v>8.387323943661983</v>
       </c>
       <c r="N36" t="n">
-        <v>1.040916268564233</v>
+        <v>10.40916268564233</v>
       </c>
       <c r="O36" t="n">
-        <v>0.9578734572408468</v>
+        <v>9.578734572408468</v>
       </c>
       <c r="P36" t="n">
         <v>0.9202214300695585</v>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3.425170068027211</v>
+        <v>34.25170068027211</v>
       </c>
       <c r="D37" t="n">
-        <v>2.508969341161122</v>
+        <v>25.08969341161122</v>
       </c>
       <c r="E37" t="n">
         <v>1496</v>
@@ -2556,10 +2556,10 @@
         <v>37.29193548387099</v>
       </c>
       <c r="N37" t="n">
-        <v>1.254484670580561</v>
+        <v>12.54484670580561</v>
       </c>
       <c r="O37" t="n">
-        <v>0.8852575865818385</v>
+        <v>8.852575865818386</v>
       </c>
       <c r="P37" t="n">
         <v>0.7056742958621818</v>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.6496598639455783</v>
+        <v>6.496598639455783</v>
       </c>
       <c r="D38" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E38" t="n">
         <v>1523.2</v>
@@ -2613,10 +2613,10 @@
         <v>22</v>
       </c>
       <c r="N38" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O38" t="n">
-        <v>1.061089782447632</v>
+        <v>10.61089782447633</v>
       </c>
       <c r="P38" t="n">
         <v>0.8296819043606488</v>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4.438775510204081</v>
+        <v>44.38775510204081</v>
       </c>
       <c r="D39" t="n">
-        <v>2.402665175659304</v>
+        <v>24.02665175659304</v>
       </c>
       <c r="E39" t="n">
         <v>1018.897297297297</v>
@@ -2670,10 +2670,10 @@
         <v>22.83709677419353</v>
       </c>
       <c r="N39" t="n">
-        <v>1.201332587829652</v>
+        <v>12.01332587829652</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9752227187782311</v>
+        <v>9.75222718778231</v>
       </c>
       <c r="P39" t="n">
         <v>0.8117841209486251</v>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3.510204081632653</v>
+        <v>35.10204081632653</v>
       </c>
       <c r="D40" t="n">
-        <v>2.499953406019942</v>
+        <v>24.99953406019942</v>
       </c>
       <c r="E40" t="n">
         <v>1142.4</v>
@@ -2727,10 +2727,10 @@
         <v>18.86451612903227</v>
       </c>
       <c r="N40" t="n">
-        <v>1.249976703009971</v>
+        <v>12.49976703009971</v>
       </c>
       <c r="O40" t="n">
-        <v>1.06319931559381</v>
+        <v>10.6319931559381</v>
       </c>
       <c r="P40" t="n">
         <v>0.8505753051505704</v>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3.030612244897959</v>
+        <v>30.30612244897959</v>
       </c>
       <c r="D41" t="n">
-        <v>2.552581306495201</v>
+        <v>25.52581306495201</v>
       </c>
       <c r="E41" t="n">
         <v>1322.778947368421</v>
@@ -2784,10 +2784,10 @@
         <v>14.22419354838712</v>
       </c>
       <c r="N41" t="n">
-        <v>1.2762906532476</v>
+        <v>12.762906532476</v>
       </c>
       <c r="O41" t="n">
-        <v>1.135457053758619</v>
+        <v>11.35457053758619</v>
       </c>
       <c r="P41" t="n">
         <v>0.8896539756593675</v>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3.068027210884354</v>
+        <v>30.68027210884354</v>
       </c>
       <c r="D42" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E42" t="n">
         <v>2056.32</v>
@@ -2841,10 +2841,10 @@
         <v>29.47903225806454</v>
       </c>
       <c r="N42" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O42" t="n">
-        <v>0.9870399581103599</v>
+        <v>9.8703995811036</v>
       </c>
       <c r="P42" t="n">
         <v>0.7717812438416112</v>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6.738095238095238</v>
+        <v>67.38095238095238</v>
       </c>
       <c r="D43" t="n">
-        <v>2.083781406784066</v>
+        <v>20.83781406784066</v>
       </c>
       <c r="E43" t="n">
         <v>1428</v>
@@ -2898,10 +2898,10 @@
         <v>9.105633802816897</v>
       </c>
       <c r="N43" t="n">
-        <v>1.041890703392033</v>
+        <v>10.41890703392033</v>
       </c>
       <c r="O43" t="n">
-        <v>0.9517359132651327</v>
+        <v>9.517359132651327</v>
       </c>
       <c r="P43" t="n">
         <v>0.9134700119375406</v>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8.336734693877549</v>
+        <v>83.36734693877548</v>
       </c>
       <c r="D44" t="n">
-        <v>1.898638789502089</v>
+        <v>18.98638789502089</v>
       </c>
       <c r="E44" t="n">
         <v>2154.24</v>
@@ -2955,10 +2955,10 @@
         <v>7.649452269170581</v>
       </c>
       <c r="N44" t="n">
-        <v>0.9493193947510445</v>
+        <v>9.493193947510445</v>
       </c>
       <c r="O44" t="n">
-        <v>0.8735822435711378</v>
+        <v>8.735822435711377</v>
       </c>
       <c r="P44" t="n">
         <v>0.9202195261166359</v>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6.833333333333333</v>
+        <v>68.33333333333333</v>
       </c>
       <c r="D45" t="n">
-        <v>2.080273441403986</v>
+        <v>20.80273441403986</v>
       </c>
       <c r="E45" t="n">
         <v>1122</v>
@@ -3012,10 +3012,10 @@
         <v>16.55712050078247</v>
       </c>
       <c r="N45" t="n">
-        <v>1.040136720701993</v>
+        <v>10.40136720701993</v>
       </c>
       <c r="O45" t="n">
-        <v>0.8762048345556317</v>
+        <v>8.762048345556316</v>
       </c>
       <c r="P45" t="n">
         <v>0.8423939056437477</v>
@@ -3036,10 +3036,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>9.064625850340136</v>
+        <v>90.64625850340136</v>
       </c>
       <c r="D46" t="n">
-        <v>1.820878890243659</v>
+        <v>18.20878890243659</v>
       </c>
       <c r="E46" t="n">
         <v>1216.103225806452</v>
@@ -3069,10 +3069,10 @@
         <v>9.471830985915489</v>
       </c>
       <c r="N46" t="n">
-        <v>0.9104394451218295</v>
+        <v>9.104394451218296</v>
       </c>
       <c r="O46" t="n">
-        <v>0.8166589403107851</v>
+        <v>8.166589403107851</v>
       </c>
       <c r="P46" t="n">
         <v>0.8969942423809468</v>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6.928571428571428</v>
+        <v>69.28571428571428</v>
       </c>
       <c r="D47" t="n">
-        <v>2.063902936296948</v>
+        <v>20.63902936296948</v>
       </c>
       <c r="E47" t="n">
         <v>1365.913043478261</v>
@@ -3126,10 +3126,10 @@
         <v>10.54773082942097</v>
       </c>
       <c r="N47" t="n">
-        <v>1.031951468148474</v>
+        <v>10.31951468148474</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9275184896393552</v>
+        <v>9.275184896393553</v>
       </c>
       <c r="P47" t="n">
         <v>0.8988004942747045</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6.612244897959184</v>
+        <v>66.12244897959184</v>
       </c>
       <c r="D48" t="n">
-        <v>2.107947390513503</v>
+        <v>21.07947390513502</v>
       </c>
       <c r="E48" t="n">
         <v>1092.730434782609</v>
@@ -3183,10 +3183,10 @@
         <v>9.318466353677621</v>
       </c>
       <c r="N48" t="n">
-        <v>1.053973695256751</v>
+        <v>10.53973695256751</v>
       </c>
       <c r="O48" t="n">
-        <v>0.9617116521510322</v>
+        <v>9.617116521510322</v>
       </c>
       <c r="P48" t="n">
         <v>0.9124626700638447</v>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6.472789115646258</v>
+        <v>64.72789115646259</v>
       </c>
       <c r="D49" t="n">
-        <v>2.11925083451598</v>
+        <v>21.1925083451598</v>
       </c>
       <c r="E49" t="n">
         <v>753.9839999999999</v>
@@ -3240,10 +3240,10 @@
         <v>7.172926447574326</v>
       </c>
       <c r="N49" t="n">
-        <v>1.05962541725799</v>
+        <v>10.5962541725799</v>
       </c>
       <c r="O49" t="n">
-        <v>0.9886063435196305</v>
+        <v>9.886063435196306</v>
       </c>
       <c r="P49" t="n">
         <v>0.9329771893145627</v>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7.095238095238096</v>
+        <v>70.95238095238096</v>
       </c>
       <c r="D50" t="n">
-        <v>2.04558356153431</v>
+        <v>20.4558356153431</v>
       </c>
       <c r="E50" t="n">
         <v>1698.162162162162</v>
@@ -3297,10 +3297,10 @@
         <v>7.543818466353684</v>
       </c>
       <c r="N50" t="n">
-        <v>1.022791780767155</v>
+        <v>10.22791780767155</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9481005088230591</v>
+        <v>9.481005088230591</v>
       </c>
       <c r="P50" t="n">
         <v>0.9269731402338088</v>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8.85034013605442</v>
+        <v>88.5034013605442</v>
       </c>
       <c r="D51" t="n">
-        <v>1.842901117351936</v>
+        <v>18.42901117351936</v>
       </c>
       <c r="E51" t="n">
         <v>1396.266666666667</v>
@@ -3354,10 +3354,10 @@
         <v>7.248043818466357</v>
       </c>
       <c r="N51" t="n">
-        <v>0.9214505586759678</v>
+        <v>9.214505586759678</v>
       </c>
       <c r="O51" t="n">
-        <v>0.8496877485921425</v>
+        <v>8.496877485921425</v>
       </c>
       <c r="P51" t="n">
         <v>0.9221197389180149</v>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7.319727891156462</v>
+        <v>73.19727891156462</v>
       </c>
       <c r="D52" t="n">
-        <v>2.022781786563793</v>
+        <v>20.22781786563793</v>
       </c>
       <c r="E52" t="n">
         <v>1628.977777777778</v>
@@ -3411,10 +3411,10 @@
         <v>6.786384976525824</v>
       </c>
       <c r="N52" t="n">
-        <v>1.011390893281896</v>
+        <v>10.11390893281897</v>
       </c>
       <c r="O52" t="n">
-        <v>0.9441989628212447</v>
+        <v>9.441989628212447</v>
       </c>
       <c r="P52" t="n">
         <v>0.9335648255219914</v>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9.353741496598639</v>
+        <v>93.53741496598639</v>
       </c>
       <c r="D53" t="n">
-        <v>1.792230506306343</v>
+        <v>17.92230506306343</v>
       </c>
       <c r="E53" t="n">
         <v>1358.52972972973</v>
@@ -3468,10 +3468,10 @@
         <v>12.30751173708921</v>
       </c>
       <c r="N53" t="n">
-        <v>0.8961152531531713</v>
+        <v>8.961152531531713</v>
       </c>
       <c r="O53" t="n">
-        <v>0.7742587013008028</v>
+        <v>7.742587013008028</v>
       </c>
       <c r="P53" t="n">
         <v>0.8640168757047819</v>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7.806122448979592</v>
+        <v>78.06122448979592</v>
       </c>
       <c r="D54" t="n">
-        <v>1.960807731515721</v>
+        <v>19.60807731515721</v>
       </c>
       <c r="E54" t="n">
         <v>1933.292307692308</v>
@@ -3525,10 +3525,10 @@
         <v>10.2300469483568</v>
       </c>
       <c r="N54" t="n">
-        <v>0.9804038657578605</v>
+        <v>9.804038657578605</v>
       </c>
       <c r="O54" t="n">
-        <v>0.8791162722097734</v>
+        <v>8.791162722097734</v>
       </c>
       <c r="P54" t="n">
         <v>0.896687888445043</v>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3.561224489795918</v>
+        <v>35.61224489795918</v>
       </c>
       <c r="D55" t="n">
-        <v>2.481502189917063</v>
+        <v>24.81502189917063</v>
       </c>
       <c r="E55" t="n">
         <v>819.5478260869564</v>
@@ -3582,10 +3582,10 @@
         <v>27.4548387096774</v>
       </c>
       <c r="N55" t="n">
-        <v>1.240751094958531</v>
+        <v>12.40751094958531</v>
       </c>
       <c r="O55" t="n">
-        <v>0.9689210087241015</v>
+        <v>9.689210087241015</v>
       </c>
       <c r="P55" t="n">
         <v>0.7809148931329253</v>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.629251700680272</v>
+        <v>16.29251700680272</v>
       </c>
       <c r="D56" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E56" t="n">
         <v>1216.103225806452</v>
@@ -3639,10 +3639,10 @@
         <v>12</v>
       </c>
       <c r="N56" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O56" t="n">
-        <v>1.160099683437732</v>
+        <v>11.60099683437732</v>
       </c>
       <c r="P56" t="n">
         <v>0.907099220560354</v>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2.459183673469388</v>
+        <v>24.59183673469388</v>
       </c>
       <c r="D57" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E57" t="n">
         <v>1523.2</v>
@@ -3696,10 +3696,10 @@
         <v>10.5</v>
       </c>
       <c r="N57" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O57" t="n">
-        <v>1.174951168586246</v>
+        <v>11.74951168586246</v>
       </c>
       <c r="P57" t="n">
         <v>0.9187118179903097</v>
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.4285714285714285</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="D58" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E58" t="n">
         <v>1396.266666666667</v>
@@ -3753,10 +3753,10 @@
         <v>35</v>
       </c>
       <c r="N58" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O58" t="n">
-        <v>0.9323769111605037</v>
+        <v>9.323769111605037</v>
       </c>
       <c r="P58" t="n">
         <v>0.7290393933010322</v>
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5.581632653061225</v>
+        <v>55.81632653061224</v>
       </c>
       <c r="D59" t="n">
-        <v>2.239539651477029</v>
+        <v>22.39539651477029</v>
       </c>
       <c r="E59" t="n">
         <v>1225.990243902439</v>
@@ -3810,10 +3810,10 @@
         <v>34.08387096774194</v>
       </c>
       <c r="N59" t="n">
-        <v>1.119769825738514</v>
+        <v>11.19769825738515</v>
       </c>
       <c r="O59" t="n">
-        <v>0.7823057567509705</v>
+        <v>7.823057567509704</v>
       </c>
       <c r="P59" t="n">
         <v>0.6986308603511632</v>
@@ -3834,10 +3834,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.7448979591836735</v>
+        <v>7.448979591836736</v>
       </c>
       <c r="D60" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E60" t="n">
         <v>1795.2</v>
@@ -3867,10 +3867,10 @@
         <v>16.5</v>
       </c>
       <c r="N60" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O60" t="n">
-        <v>1.115545227992187</v>
+        <v>11.15545227992187</v>
       </c>
       <c r="P60" t="n">
         <v>0.8722614282704867</v>
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6.115646258503402</v>
+        <v>61.15646258503402</v>
       </c>
       <c r="D61" t="n">
-        <v>2.177266797129811</v>
+        <v>21.77266797129811</v>
       </c>
       <c r="E61" t="n">
         <v>1102.315789473684</v>
@@ -3924,10 +3924,10 @@
         <v>23.77580645161291</v>
       </c>
       <c r="N61" t="n">
-        <v>1.088633398564905</v>
+        <v>10.88633398564905</v>
       </c>
       <c r="O61" t="n">
-        <v>0.8532293742915102</v>
+        <v>8.532293742915103</v>
       </c>
       <c r="P61" t="n">
         <v>0.7837618939638291</v>
@@ -3948,10 +3948,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.3877551020408163</v>
+        <v>3.877551020408163</v>
       </c>
       <c r="D62" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E62" t="n">
         <v>1216.103225806452</v>
@@ -3981,10 +3981,10 @@
         <v>14.5</v>
       </c>
       <c r="N62" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O62" t="n">
-        <v>1.135347208190207</v>
+        <v>11.35347208190207</v>
       </c>
       <c r="P62" t="n">
         <v>0.8877448915104276</v>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5.040816326530612</v>
+        <v>50.40816326530611</v>
       </c>
       <c r="D63" t="n">
-        <v>2.312296151337248</v>
+        <v>23.12296151337247</v>
       </c>
       <c r="E63" t="n">
         <v>1018.897297297297</v>
@@ -4038,10 +4038,10 @@
         <v>12.69032258064516</v>
       </c>
       <c r="N63" t="n">
-        <v>1.156148075668624</v>
+        <v>11.56148075668624</v>
       </c>
       <c r="O63" t="n">
-        <v>1.030501317444414</v>
+        <v>10.30501317444414</v>
       </c>
       <c r="P63" t="n">
         <v>0.891322953462042</v>
@@ -4062,10 +4062,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4.976190476190476</v>
+        <v>49.76190476190476</v>
       </c>
       <c r="D64" t="n">
-        <v>2.322570123939987</v>
+        <v>23.22570123939987</v>
       </c>
       <c r="E64" t="n">
         <v>1309</v>
@@ -4095,10 +4095,10 @@
         <v>9.199999999999989</v>
       </c>
       <c r="N64" t="n">
-        <v>1.161285061969994</v>
+        <v>11.61285061969994</v>
       </c>
       <c r="O64" t="n">
-        <v>1.070195953059103</v>
+        <v>10.70195953059103</v>
       </c>
       <c r="P64" t="n">
         <v>0.9215618008929106</v>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2.928571428571428</v>
+        <v>29.28571428571428</v>
       </c>
       <c r="D65" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E65" t="n">
         <v>1523.2</v>
@@ -4152,10 +4152,10 @@
         <v>10.34677419354841</v>
       </c>
       <c r="N65" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O65" t="n">
-        <v>1.176468255778836</v>
+        <v>11.76468255778836</v>
       </c>
       <c r="P65" t="n">
         <v>0.9198980510611113</v>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.965986394557823</v>
+        <v>19.65986394557823</v>
       </c>
       <c r="D66" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E66" t="n">
         <v>1142.4</v>
@@ -4209,10 +4209,10 @@
         <v>13.5</v>
       </c>
       <c r="N66" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O66" t="n">
-        <v>1.145248198289217</v>
+        <v>11.45248198289217</v>
       </c>
       <c r="P66" t="n">
         <v>0.8954866231303982</v>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4.340136054421769</v>
+        <v>43.40136054421769</v>
       </c>
       <c r="D67" t="n">
-        <v>2.405390923492685</v>
+        <v>24.05390923492685</v>
       </c>
       <c r="E67" t="n">
         <v>1256.64</v>
@@ -4266,10 +4266,10 @@
         <v>10.45967741935482</v>
       </c>
       <c r="N67" t="n">
-        <v>1.202695461746342</v>
+        <v>12.02695461746342</v>
       </c>
       <c r="O67" t="n">
-        <v>1.099134299178473</v>
+        <v>10.99134299178473</v>
       </c>
       <c r="P67" t="n">
         <v>0.9138924475382187</v>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.9115646258503401</v>
+        <v>9.115646258503402</v>
       </c>
       <c r="D68" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E68" t="n">
         <v>1478.4</v>
@@ -4323,10 +4323,10 @@
         <v>15.5</v>
       </c>
       <c r="N68" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O68" t="n">
-        <v>1.125446218091197</v>
+        <v>11.25446218091197</v>
       </c>
       <c r="P68" t="n">
         <v>0.8800031598904572</v>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.4353741496598639</v>
+        <v>4.353741496598639</v>
       </c>
       <c r="D69" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E69" t="n">
         <v>2026.838709677419</v>
@@ -4380,10 +4380,10 @@
         <v>30</v>
       </c>
       <c r="N69" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O69" t="n">
-        <v>0.9818818616555534</v>
+        <v>9.818818616555534</v>
       </c>
       <c r="P69" t="n">
         <v>0.7677480514008848</v>
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.5170068027210885</v>
+        <v>5.170068027210885</v>
       </c>
       <c r="D70" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E70" t="n">
         <v>1532.487804878049</v>
@@ -4437,10 +4437,10 @@
         <v>16</v>
       </c>
       <c r="N70" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O70" t="n">
-        <v>1.120495723041692</v>
+        <v>11.20495723041692</v>
       </c>
       <c r="P70" t="n">
         <v>0.8761322940804719</v>
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3.312925170068027</v>
+        <v>33.12925170068027</v>
       </c>
       <c r="D71" t="n">
-        <v>2.529517286366601</v>
+        <v>25.29517286366601</v>
       </c>
       <c r="E71" t="n">
         <v>1436.16</v>
@@ -4494,10 +4494,10 @@
         <v>9.333870967741916</v>
       </c>
       <c r="N71" t="n">
-        <v>1.264758643183301</v>
+        <v>12.64758643183301</v>
       </c>
       <c r="O71" t="n">
-        <v>1.172344079146252</v>
+        <v>11.72344079146252</v>
       </c>
       <c r="P71" t="n">
         <v>0.926931067413425</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2.959183673469388</v>
+        <v>29.59183673469388</v>
       </c>
       <c r="D72" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E72" t="n">
         <v>1933.292307692308</v>
@@ -4551,10 +4551,10 @@
         <v>30.60161290322583</v>
       </c>
       <c r="N72" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O72" t="n">
-        <v>0.9759252982572777</v>
+        <v>9.759252982572777</v>
       </c>
       <c r="P72" t="n">
         <v>0.7630905257649991</v>
@@ -4575,10 +4575,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.3163265306122449</v>
+        <v>3.163265306122449</v>
       </c>
       <c r="D73" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E73" t="n">
         <v>2037.794594594594</v>
@@ -4608,10 +4608,10 @@
         <v>18</v>
       </c>
       <c r="N73" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O73" t="n">
-        <v>1.100693742843672</v>
+        <v>11.00693742843672</v>
       </c>
       <c r="P73" t="n">
         <v>0.8606488308405309</v>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.346938775510204</v>
+        <v>13.46938775510204</v>
       </c>
       <c r="D74" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E74" t="n">
         <v>1256.64</v>
@@ -4665,10 +4665,10 @@
         <v>12</v>
       </c>
       <c r="N74" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O74" t="n">
-        <v>1.160099683437732</v>
+        <v>11.60099683437732</v>
       </c>
       <c r="P74" t="n">
         <v>0.907099220560354</v>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.4591836734693878</v>
+        <v>4.591836734693878</v>
       </c>
       <c r="D75" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E75" t="n">
         <v>1108.8</v>
@@ -4722,10 +4722,10 @@
         <v>18.5</v>
       </c>
       <c r="N75" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O75" t="n">
-        <v>1.095743247794167</v>
+        <v>10.95743247794167</v>
       </c>
       <c r="P75" t="n">
         <v>0.8567779650305457</v>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4.751700680272108</v>
+        <v>47.51700680272108</v>
       </c>
       <c r="D76" t="n">
-        <v>2.357166154132886</v>
+        <v>23.57166154132886</v>
       </c>
       <c r="E76" t="n">
         <v>1142.4</v>
@@ -4779,10 +4779,10 @@
         <v>11.94677419354838</v>
       </c>
       <c r="N76" t="n">
-        <v>1.178583077066443</v>
+        <v>11.78583077066443</v>
       </c>
       <c r="O76" t="n">
-        <v>1.060298184061013</v>
+        <v>10.60298184061013</v>
       </c>
       <c r="P76" t="n">
         <v>0.8996380524147292</v>
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6.112244897959184</v>
+        <v>61.12244897959184</v>
       </c>
       <c r="D77" t="n">
-        <v>2.183137638617091</v>
+        <v>21.83137638617091</v>
       </c>
       <c r="E77" t="n">
         <v>1795.2</v>
@@ -4836,10 +4836,10 @@
         <v>16.65322580645162</v>
       </c>
       <c r="N77" t="n">
-        <v>1.091568819308545</v>
+        <v>10.91568819308545</v>
       </c>
       <c r="O77" t="n">
-        <v>0.9266853954822917</v>
+        <v>9.266853954822917</v>
       </c>
       <c r="P77" t="n">
         <v>0.8489482102184825</v>
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3.751700680272109</v>
+        <v>37.51700680272109</v>
       </c>
       <c r="D78" t="n">
-        <v>2.464309011275743</v>
+        <v>24.64309011275743</v>
       </c>
       <c r="E78" t="n">
         <v>785.4</v>
@@ -4893,10 +4893,10 @@
         <v>12.19838709677418</v>
       </c>
       <c r="N78" t="n">
-        <v>1.232154505637871</v>
+        <v>12.32154505637871</v>
       </c>
       <c r="O78" t="n">
-        <v>1.11137839576882</v>
+        <v>11.1137839576882</v>
       </c>
       <c r="P78" t="n">
         <v>0.9019797360506124</v>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8.884353741496598</v>
+        <v>88.84353741496598</v>
       </c>
       <c r="D79" t="n">
-        <v>1.840172699834096</v>
+        <v>18.40172699834096</v>
       </c>
       <c r="E79" t="n">
         <v>1733.296551724138</v>
@@ -4950,10 +4950,10 @@
         <v>9.442097026604074</v>
       </c>
       <c r="N79" t="n">
-        <v>0.9200863499170481</v>
+        <v>9.200863499170481</v>
       </c>
       <c r="O79" t="n">
-        <v>0.8266002407427504</v>
+        <v>8.266002407427504</v>
       </c>
       <c r="P79" t="n">
         <v>0.8983942005196294</v>
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>7.428571428571428</v>
+        <v>74.28571428571428</v>
       </c>
       <c r="D80" t="n">
-        <v>1.996666933178756</v>
+        <v>19.96666933178756</v>
       </c>
       <c r="E80" t="n">
         <v>876.7255813953487</v>
@@ -5007,10 +5007,10 @@
         <v>17.29186228482004</v>
       </c>
       <c r="N80" t="n">
-        <v>0.9983334665893782</v>
+        <v>9.983334665893782</v>
       </c>
       <c r="O80" t="n">
-        <v>0.8271269093139322</v>
+        <v>8.271269093139322</v>
       </c>
       <c r="P80" t="n">
         <v>0.8285076449852558</v>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1.602040816326531</v>
+        <v>16.02040816326531</v>
       </c>
       <c r="D81" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E81" t="n">
         <v>2217.6</v>
@@ -5064,10 +5064,10 @@
         <v>12</v>
       </c>
       <c r="N81" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O81" t="n">
-        <v>1.160099683437732</v>
+        <v>11.60099683437732</v>
       </c>
       <c r="P81" t="n">
         <v>0.907099220560354</v>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6.112244897959184</v>
+        <v>61.12244897959184</v>
       </c>
       <c r="D82" t="n">
-        <v>2.172653993104091</v>
+        <v>21.72653993104091</v>
       </c>
       <c r="E82" t="n">
         <v>1322.778947368421</v>
@@ -5121,10 +5121,10 @@
         <v>11.5</v>
       </c>
       <c r="N82" t="n">
-        <v>1.086326996552045</v>
+        <v>10.86326996552046</v>
       </c>
       <c r="O82" t="n">
-        <v>0.9724656104134315</v>
+        <v>9.724656104134315</v>
       </c>
       <c r="P82" t="n">
         <v>0.895186820819141</v>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>4.363945578231292</v>
+        <v>43.63945578231292</v>
       </c>
       <c r="D83" t="n">
-        <v>2.406019942223464</v>
+        <v>24.06019942223464</v>
       </c>
       <c r="E83" t="n">
         <v>1256.64</v>
@@ -5178,10 +5178,10 @@
         <v>13.05161290322582</v>
       </c>
       <c r="N83" t="n">
-        <v>1.203009971111732</v>
+        <v>12.03009971111732</v>
       </c>
       <c r="O83" t="n">
-        <v>1.073786080980783</v>
+        <v>10.73786080980783</v>
       </c>
       <c r="P83" t="n">
         <v>0.8925828602970517</v>
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2.527210884353742</v>
+        <v>25.27210884353742</v>
       </c>
       <c r="D84" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E84" t="n">
         <v>1256.64</v>
@@ -5235,10 +5235,10 @@
         <v>14.5</v>
       </c>
       <c r="N84" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O84" t="n">
-        <v>1.135347208190207</v>
+        <v>11.35347208190207</v>
       </c>
       <c r="P84" t="n">
         <v>0.8877448915104276</v>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>5.98639455782313</v>
+        <v>59.8639455782313</v>
       </c>
       <c r="D85" t="n">
-        <v>2.18355698443761</v>
+        <v>21.8355698443761</v>
       </c>
       <c r="E85" t="n">
         <v>1018.897297297297</v>
@@ -5292,10 +5292,10 @@
         <v>16.03064516129032</v>
       </c>
       <c r="N85" t="n">
-        <v>1.091778492218805</v>
+        <v>10.91778492218805</v>
       </c>
       <c r="O85" t="n">
-        <v>0.9330592331961286</v>
+        <v>9.330592331961286</v>
       </c>
       <c r="P85" t="n">
         <v>0.8546232041079013</v>
@@ -5316,10 +5316,10 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4.061224489795919</v>
+        <v>40.61224489795919</v>
       </c>
       <c r="D86" t="n">
-        <v>2.434954803839344</v>
+        <v>24.34954803839344</v>
       </c>
       <c r="E86" t="n">
         <v>1478.4</v>
@@ -5349,10 +5349,10 @@
         <v>11.20645161290321</v>
       </c>
       <c r="N86" t="n">
-        <v>1.217477401919672</v>
+        <v>12.17477401919672</v>
       </c>
       <c r="O86" t="n">
-        <v>1.106522435455284</v>
+        <v>11.06522435455284</v>
       </c>
       <c r="P86" t="n">
         <v>0.9088648657548479</v>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4.142857142857143</v>
+        <v>41.42857142857143</v>
       </c>
       <c r="D87" t="n">
-        <v>2.432229056005964</v>
+        <v>24.32229056005964</v>
       </c>
       <c r="E87" t="n">
         <v>2393.6</v>
@@ -5406,10 +5406,10 @@
         <v>9.716129032258038</v>
       </c>
       <c r="N87" t="n">
-        <v>1.216114528002982</v>
+        <v>12.16114528002982</v>
       </c>
       <c r="O87" t="n">
-        <v>1.119915230653892</v>
+        <v>11.19915230653892</v>
       </c>
       <c r="P87" t="n">
         <v>0.9208961860631159</v>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>5.04421768707483</v>
+        <v>50.4421768707483</v>
       </c>
       <c r="D88" t="n">
-        <v>2.311457459696207</v>
+        <v>23.11457459696207</v>
       </c>
       <c r="E88" t="n">
         <v>1461.209302325581</v>
@@ -5463,10 +5463,10 @@
         <v>8.454838709677404</v>
       </c>
       <c r="N88" t="n">
-        <v>1.155728729848103</v>
+        <v>11.55728729848103</v>
       </c>
       <c r="O88" t="n">
-        <v>1.072017455494862</v>
+        <v>10.72017455494862</v>
       </c>
       <c r="P88" t="n">
         <v>0.9275684058107271</v>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5.748299319727892</v>
+        <v>57.48299319727892</v>
       </c>
       <c r="D89" t="n">
-        <v>2.223604510297269</v>
+        <v>22.23604510297269</v>
       </c>
       <c r="E89" t="n">
         <v>1108.8</v>
@@ -5520,10 +5520,10 @@
         <v>13.66451612903225</v>
       </c>
       <c r="N89" t="n">
-        <v>1.111802255148635</v>
+        <v>11.11802255148635</v>
       </c>
       <c r="O89" t="n">
-        <v>0.9765100162473253</v>
+        <v>9.765100162473253</v>
       </c>
       <c r="P89" t="n">
         <v>0.8783126781090919</v>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3.431972789115646</v>
+        <v>34.31972789115646</v>
       </c>
       <c r="D90" t="n">
-        <v>2.501630789302022</v>
+        <v>25.01630789302023</v>
       </c>
       <c r="E90" t="n">
         <v>2037.794594594594</v>
@@ -5577,10 +5577,10 @@
         <v>9.343548387096746</v>
       </c>
       <c r="N90" t="n">
-        <v>1.250815394651011</v>
+        <v>12.50815394651011</v>
       </c>
       <c r="O90" t="n">
-        <v>1.158305014580747</v>
+        <v>11.58305014580747</v>
       </c>
       <c r="P90" t="n">
         <v>0.926039941252821</v>
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3.391156462585034</v>
+        <v>33.91156462585034</v>
       </c>
       <c r="D91" t="n">
-        <v>2.512743453545802</v>
+        <v>25.12743453545802</v>
       </c>
       <c r="E91" t="n">
         <v>1478.4</v>
@@ -5634,10 +5634,10 @@
         <v>11.02741935483868</v>
       </c>
       <c r="N91" t="n">
-        <v>1.256371726772901</v>
+        <v>12.56371726772901</v>
       </c>
       <c r="O91" t="n">
-        <v>1.147189356923013</v>
+        <v>11.47189356923013</v>
       </c>
       <c r="P91" t="n">
         <v>0.9130970814423433</v>
@@ -5658,10 +5658,10 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5.989795918367347</v>
+        <v>59.89795918367346</v>
       </c>
       <c r="D92" t="n">
-        <v>2.180202217873451</v>
+        <v>21.80202217873451</v>
       </c>
       <c r="E92" t="n">
         <v>1288.861538461538</v>
@@ -5691,10 +5691,10 @@
         <v>10.24516129032259</v>
       </c>
       <c r="N92" t="n">
-        <v>1.090101108936725</v>
+        <v>10.90101108936725</v>
       </c>
       <c r="O92" t="n">
-        <v>0.988663868438482</v>
+        <v>9.88663868438482</v>
       </c>
       <c r="P92" t="n">
         <v>0.906946943116878</v>
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5.289115646258503</v>
+        <v>52.89115646258503</v>
       </c>
       <c r="D93" t="n">
-        <v>2.274974373310968</v>
+        <v>22.74974373310968</v>
       </c>
       <c r="E93" t="n">
         <v>1299.972413793103</v>
@@ -5748,10 +5748,10 @@
         <v>14.36290322580646</v>
       </c>
       <c r="N93" t="n">
-        <v>1.137487186655484</v>
+        <v>11.37487186655484</v>
       </c>
       <c r="O93" t="n">
-        <v>0.9952802240237369</v>
+        <v>9.95280224023737</v>
       </c>
       <c r="P93" t="n">
         <v>0.8749814817256328</v>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5.812925170068027</v>
+        <v>58.12925170068027</v>
       </c>
       <c r="D94" t="n">
-        <v>2.21773366880999</v>
+        <v>22.1773366880999</v>
       </c>
       <c r="E94" t="n">
         <v>1396.266666666667</v>
@@ -5805,10 +5805,10 @@
         <v>8.612903225806463</v>
       </c>
       <c r="N94" t="n">
-        <v>1.108866834404995</v>
+        <v>11.08866834404995</v>
       </c>
       <c r="O94" t="n">
-        <v>1.023590564842555</v>
+        <v>10.23590564842555</v>
       </c>
       <c r="P94" t="n">
         <v>0.9230960229699733</v>
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5.751700680272108</v>
+        <v>57.51700680272108</v>
       </c>
       <c r="D95" t="n">
-        <v>2.22381418320753</v>
+        <v>22.2381418320753</v>
       </c>
       <c r="E95" t="n">
         <v>1322.778947368421</v>
@@ -5862,10 +5862,10 @@
         <v>8.072580645161281</v>
       </c>
       <c r="N95" t="n">
-        <v>1.111907091603765</v>
+        <v>11.11907091603765</v>
       </c>
       <c r="O95" t="n">
-        <v>1.031980550562564</v>
+        <v>10.31980550562564</v>
       </c>
       <c r="P95" t="n">
         <v>0.9281176083462888</v>
@@ -5886,10 +5886,10 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3.08843537414966</v>
+        <v>30.8843537414966</v>
       </c>
       <c r="D96" t="n">
-        <v>2.537904202777001</v>
+        <v>25.37904202777001</v>
       </c>
       <c r="E96" t="n">
         <v>1621.470967741936</v>
@@ -5919,10 +5919,10 @@
         <v>8.774193548387075</v>
       </c>
       <c r="N96" t="n">
-        <v>1.268952101388501</v>
+        <v>12.68952101388501</v>
       </c>
       <c r="O96" t="n">
-        <v>1.182078897939124</v>
+        <v>11.82078897939124</v>
       </c>
       <c r="P96" t="n">
         <v>0.9315394148019304</v>
@@ -5943,10 +5943,10 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5.384353741496598</v>
+        <v>53.84353741496598</v>
       </c>
       <c r="D97" t="n">
-        <v>2.261135961233809</v>
+        <v>22.61135961233809</v>
       </c>
       <c r="E97" t="n">
         <v>1570.8</v>
@@ -5976,10 +5976,10 @@
         <v>8.809677419354841</v>
       </c>
       <c r="N97" t="n">
-        <v>1.130567980616904</v>
+        <v>11.30567980616904</v>
       </c>
       <c r="O97" t="n">
-        <v>1.043343451712401</v>
+        <v>10.43343451712401</v>
       </c>
       <c r="P97" t="n">
         <v>0.9228489304491814</v>
@@ -6000,10 +6000,10 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4.316326530612245</v>
+        <v>43.16326530612245</v>
       </c>
       <c r="D98" t="n">
-        <v>2.404761904761905</v>
+        <v>24.04761904761905</v>
       </c>
       <c r="E98" t="n">
         <v>1449.969230769231</v>
@@ -6033,10 +6033,10 @@
         <v>10.45967741935482</v>
       </c>
       <c r="N98" t="n">
-        <v>1.202380952380952</v>
+        <v>12.02380952380952</v>
       </c>
       <c r="O98" t="n">
-        <v>1.098819789813083</v>
+        <v>10.98819789813083</v>
       </c>
       <c r="P98" t="n">
         <v>0.9138699242009799</v>
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5.275510204081633</v>
+        <v>52.75510204081633</v>
       </c>
       <c r="D99" t="n">
-        <v>2.288603112477868</v>
+        <v>22.88603112477868</v>
       </c>
       <c r="E99" t="n">
         <v>992.0842105263157</v>
@@ -6090,10 +6090,10 @@
         <v>11.32096774193548</v>
       </c>
       <c r="N99" t="n">
-        <v>1.144301556238934</v>
+        <v>11.44301556238934</v>
       </c>
       <c r="O99" t="n">
-        <v>1.03221276671482</v>
+        <v>10.3221276671482</v>
       </c>
       <c r="P99" t="n">
         <v>0.9020461093380623</v>
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>6.795918367346938</v>
+        <v>67.95918367346938</v>
       </c>
       <c r="D100" t="n">
-        <v>2.077155249955026</v>
+        <v>20.77155249955026</v>
       </c>
       <c r="E100" t="n">
         <v>1256.64</v>
@@ -6147,10 +6147,10 @@
         <v>10.33881064162753</v>
       </c>
       <c r="N100" t="n">
-        <v>1.038577624977513</v>
+        <v>10.38577624977513</v>
       </c>
       <c r="O100" t="n">
-        <v>0.9362131631792208</v>
+        <v>9.362131631792208</v>
       </c>
       <c r="P100" t="n">
         <v>0.9014378325351379</v>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>6.891156462585035</v>
+        <v>68.91156462585035</v>
       </c>
       <c r="D101" t="n">
-        <v>2.084950728577425</v>
+        <v>20.84950728577425</v>
       </c>
       <c r="E101" t="n">
         <v>1178.1</v>
@@ -6204,10 +6204,10 @@
         <v>12.4600938967136</v>
       </c>
       <c r="N101" t="n">
-        <v>1.042475364288713</v>
+        <v>10.42475364288713</v>
       </c>
       <c r="O101" t="n">
-        <v>0.9191080979846175</v>
+        <v>9.191080979846175</v>
       </c>
       <c r="P101" t="n">
         <v>0.8816592981185034</v>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>6.88095238095238</v>
+        <v>68.80952380952381</v>
       </c>
       <c r="D102" t="n">
-        <v>2.072477962781587</v>
+        <v>20.72477962781587</v>
       </c>
       <c r="E102" t="n">
         <v>2166.620689655173</v>
@@ -6261,10 +6261,10 @@
         <v>8.426447574334901</v>
       </c>
       <c r="N102" t="n">
-        <v>1.036238981390793</v>
+        <v>10.36238981390793</v>
       </c>
       <c r="O102" t="n">
-        <v>0.9528088073874774</v>
+        <v>9.528088073874773</v>
       </c>
       <c r="P102" t="n">
         <v>0.9194875163918851</v>
@@ -6285,10 +6285,10 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>8.064625850340136</v>
+        <v>80.64625850340136</v>
       </c>
       <c r="D103" t="n">
-        <v>1.930405364888365</v>
+        <v>19.30405364888365</v>
       </c>
       <c r="E103" t="n">
         <v>2037.794594594594</v>
@@ -6318,10 +6318,10 @@
         <v>9.007824726134572</v>
       </c>
       <c r="N103" t="n">
-        <v>0.9652026824441823</v>
+        <v>9.652026824441823</v>
       </c>
       <c r="O103" t="n">
-        <v>0.8760162990171072</v>
+        <v>8.760162990171072</v>
       </c>
       <c r="P103" t="n">
         <v>0.9075982847444762</v>
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6.738095238095238</v>
+        <v>67.38095238095238</v>
       </c>
       <c r="D104" t="n">
-        <v>2.082806971956265</v>
+        <v>20.82806971956266</v>
       </c>
       <c r="E104" t="n">
         <v>2037.794594594594</v>
@@ -6375,10 +6375,10 @@
         <v>7.629890453834122</v>
       </c>
       <c r="N104" t="n">
-        <v>1.041403485978133</v>
+        <v>10.41403485978133</v>
       </c>
       <c r="O104" t="n">
-        <v>0.9658600161381908</v>
+        <v>9.658600161381909</v>
       </c>
       <c r="P104" t="n">
         <v>0.9274599414568042</v>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>6.306122448979592</v>
+        <v>63.06122448979592</v>
       </c>
       <c r="D105" t="n">
-        <v>2.136400887485259</v>
+        <v>21.36400887485259</v>
       </c>
       <c r="E105" t="n">
         <v>1733.296551724138</v>
@@ -6432,10 +6432,10 @@
         <v>8.449139280125195</v>
       </c>
       <c r="N105" t="n">
-        <v>1.068200443742629</v>
+        <v>10.68200443742629</v>
       </c>
       <c r="O105" t="n">
-        <v>0.9845455993849542</v>
+        <v>9.845455993849543</v>
       </c>
       <c r="P105" t="n">
         <v>0.9216861920927728</v>
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>9.605442176870747</v>
+        <v>96.05442176870747</v>
       </c>
       <c r="D106" t="n">
-        <v>1.759684383057826</v>
+        <v>17.59684383057827</v>
       </c>
       <c r="E106" t="n">
         <v>1570.8</v>
@@ -6489,10 +6489,10 @@
         <v>8.206572769953056</v>
       </c>
       <c r="N106" t="n">
-        <v>0.8798421915289132</v>
+        <v>8.798421915289133</v>
       </c>
       <c r="O106" t="n">
-        <v>0.7985889957868038</v>
+        <v>7.985889957868038</v>
       </c>
       <c r="P106" t="n">
         <v>0.9076502621442663</v>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>9.064625850340136</v>
+        <v>90.64625850340136</v>
       </c>
       <c r="D107" t="n">
-        <v>1.820684003278099</v>
+        <v>18.20684003278099</v>
       </c>
       <c r="E107" t="n">
         <v>2356.2</v>
@@ -6546,10 +6546,10 @@
         <v>7.374804381846644</v>
       </c>
       <c r="N107" t="n">
-        <v>0.9103420016390493</v>
+        <v>9.103420016390494</v>
       </c>
       <c r="O107" t="n">
-        <v>0.8373241364722508</v>
+        <v>8.373241364722508</v>
       </c>
       <c r="P107" t="n">
         <v>0.9197907324551305</v>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>7.404761904761904</v>
+        <v>74.04761904761904</v>
       </c>
       <c r="D108" t="n">
-        <v>2.013232325251354</v>
+        <v>20.13232325251354</v>
       </c>
       <c r="E108" t="n">
         <v>1733.296551724138</v>
@@ -6603,10 +6603,10 @@
         <v>17.66118935837247</v>
       </c>
       <c r="N108" t="n">
-        <v>1.006616162625677</v>
+        <v>10.06616162625677</v>
       </c>
       <c r="O108" t="n">
-        <v>0.8317529016516921</v>
+        <v>8.317529016516922</v>
       </c>
       <c r="P108" t="n">
         <v>0.8262860587119244</v>
@@ -6627,10 +6627,10 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6.826530612244897</v>
+        <v>68.26530612244898</v>
       </c>
       <c r="D109" t="n">
-        <v>2.078519458713946</v>
+        <v>20.78519458713946</v>
       </c>
       <c r="E109" t="n">
         <v>1346.4</v>
@@ -6660,10 +6660,10 @@
         <v>12.50860719874805</v>
       </c>
       <c r="N109" t="n">
-        <v>1.039259729356973</v>
+        <v>10.39259729356973</v>
       </c>
       <c r="O109" t="n">
-        <v>0.9154121333297646</v>
+        <v>9.154121333297645</v>
       </c>
       <c r="P109" t="n">
         <v>0.8808309486755179</v>
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3.755102040816327</v>
+        <v>37.55102040816327</v>
       </c>
       <c r="D110" t="n">
-        <v>2.476050694250303</v>
+        <v>24.76050694250303</v>
       </c>
       <c r="E110" t="n">
         <v>1523.2</v>
@@ -6717,10 +6717,10 @@
         <v>10.22903225806454</v>
       </c>
       <c r="N110" t="n">
-        <v>1.238025347125151</v>
+        <v>12.38025347125151</v>
       </c>
       <c r="O110" t="n">
-        <v>1.136747800015602</v>
+        <v>11.36747800015602</v>
       </c>
       <c r="P110" t="n">
         <v>0.9181942862924989</v>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4.129251700680272</v>
+        <v>41.29251700680272</v>
       </c>
       <c r="D111" t="n">
-        <v>2.442712701518964</v>
+        <v>24.42712701518964</v>
       </c>
       <c r="E111" t="n">
         <v>1047.2</v>
@@ -6774,10 +6774,10 @@
         <v>21.85967741935485</v>
       </c>
       <c r="N111" t="n">
-        <v>1.221356350759482</v>
+        <v>12.21356350759482</v>
       </c>
       <c r="O111" t="n">
-        <v>1.004923901062899</v>
+        <v>10.04923901062899</v>
       </c>
       <c r="P111" t="n">
         <v>0.8227933644738512</v>
@@ -6798,10 +6798,10 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1.908163265306122</v>
+        <v>19.08163265306122</v>
       </c>
       <c r="D112" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E112" t="n">
         <v>1436.16</v>
@@ -6831,10 +6831,10 @@
         <v>12.5</v>
       </c>
       <c r="N112" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O112" t="n">
-        <v>1.155149188388227</v>
+        <v>11.55149188388227</v>
       </c>
       <c r="P112" t="n">
         <v>0.9032283547503687</v>
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>4.510204081632653</v>
+        <v>45.10204081632654</v>
       </c>
       <c r="D113" t="n">
-        <v>2.383375267915385</v>
+        <v>23.83375267915385</v>
       </c>
       <c r="E113" t="n">
         <v>1461.209302325581</v>
@@ -6888,10 +6888,10 @@
         <v>12.00967741935483</v>
       </c>
       <c r="N113" t="n">
-        <v>1.191687633957693</v>
+        <v>11.91687633957693</v>
       </c>
       <c r="O113" t="n">
-        <v>1.072779936736358</v>
+        <v>10.72779936736358</v>
       </c>
       <c r="P113" t="n">
         <v>0.9002190726554469</v>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2.619047619047619</v>
+        <v>26.19047619047619</v>
       </c>
       <c r="D114" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E114" t="n">
         <v>1436.16</v>
@@ -6945,10 +6945,10 @@
         <v>8.5</v>
       </c>
       <c r="N114" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O114" t="n">
-        <v>1.194753148784266</v>
+        <v>11.94753148784266</v>
       </c>
       <c r="P114" t="n">
         <v>0.9341952812302506</v>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4.316326530612245</v>
+        <v>43.16326530612245</v>
       </c>
       <c r="D115" t="n">
-        <v>2.406858633864505</v>
+        <v>24.06858633864505</v>
       </c>
       <c r="E115" t="n">
         <v>1478.4</v>
@@ -7002,10 +7002,10 @@
         <v>10.49032258064517</v>
       </c>
       <c r="N115" t="n">
-        <v>1.203429316932252</v>
+        <v>12.03429316932252</v>
       </c>
       <c r="O115" t="n">
-        <v>1.099564736925865</v>
+        <v>10.99564736925864</v>
       </c>
       <c r="P115" t="n">
         <v>0.9136928288641361</v>
@@ -7026,10 +7026,10 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0.5782312925170068</v>
+        <v>5.782312925170068</v>
       </c>
       <c r="D116" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E116" t="n">
         <v>1507.968</v>
@@ -7059,10 +7059,10 @@
         <v>12.5</v>
       </c>
       <c r="N116" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O116" t="n">
-        <v>1.155149188388227</v>
+        <v>11.55149188388227</v>
       </c>
       <c r="P116" t="n">
         <v>0.9032283547503687</v>
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2.401360544217687</v>
+        <v>24.01360544217687</v>
       </c>
       <c r="D117" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E117" t="n">
         <v>1621.470967741936</v>
@@ -7116,10 +7116,10 @@
         <v>13</v>
       </c>
       <c r="N117" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O117" t="n">
-        <v>1.150198693338722</v>
+        <v>11.50198693338722</v>
       </c>
       <c r="P117" t="n">
         <v>0.8993574889403834</v>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>4.58843537414966</v>
+        <v>45.8843537414966</v>
       </c>
       <c r="D118" t="n">
-        <v>2.373730314043426</v>
+        <v>23.73730314043426</v>
       </c>
       <c r="E118" t="n">
         <v>1570.8</v>
@@ -7173,10 +7173,10 @@
         <v>9.427419354838719</v>
       </c>
       <c r="N118" t="n">
-        <v>1.186865157021713</v>
+        <v>11.86865157021713</v>
       </c>
       <c r="O118" t="n">
-        <v>1.09352437133024</v>
+        <v>10.9352437133024</v>
       </c>
       <c r="P118" t="n">
         <v>0.921355189223265</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>5.51360544217687</v>
+        <v>55.1360544217687</v>
       </c>
       <c r="D119" t="n">
-        <v>2.257781194669648</v>
+        <v>22.57781194669649</v>
       </c>
       <c r="E119" t="n">
         <v>1142.4</v>
@@ -7230,10 +7230,10 @@
         <v>9.788709677419348</v>
       </c>
       <c r="N119" t="n">
-        <v>1.128890597334824</v>
+        <v>11.28890597334824</v>
       </c>
       <c r="O119" t="n">
-        <v>1.031972679736613</v>
+        <v>10.31972679736613</v>
       </c>
       <c r="P119" t="n">
         <v>0.9141476438664448</v>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>4.047619047619047</v>
+        <v>40.47619047619047</v>
       </c>
       <c r="D120" t="n">
-        <v>2.422164756313484</v>
+        <v>24.22164756313484</v>
       </c>
       <c r="E120" t="n">
         <v>2513.28</v>
@@ -7287,10 +7287,10 @@
         <v>19.29838709677421</v>
       </c>
       <c r="N120" t="n">
-        <v>1.211082378156742</v>
+        <v>12.11082378156742</v>
       </c>
       <c r="O120" t="n">
-        <v>1.02000923858472</v>
+        <v>10.2000923858472</v>
       </c>
       <c r="P120" t="n">
         <v>0.8422294444884636</v>
@@ -7311,10 +7311,10 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3.248299319727891</v>
+        <v>32.48299319727891</v>
       </c>
       <c r="D121" t="n">
-        <v>2.524275463610102</v>
+        <v>25.24275463610102</v>
       </c>
       <c r="E121" t="n">
         <v>1933.292307692308</v>
@@ -7344,10 +7344,10 @@
         <v>8.824193548387086</v>
       </c>
       <c r="N121" t="n">
-        <v>1.262137731805051</v>
+        <v>12.62137731805051</v>
       </c>
       <c r="O121" t="n">
-        <v>1.174769478850723</v>
+        <v>11.74769478850723</v>
       </c>
       <c r="P121" t="n">
         <v>0.9307775603623089</v>
@@ -7368,10 +7368,10 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>4.870748299319728</v>
+        <v>48.70748299319728</v>
       </c>
       <c r="D122" t="n">
-        <v>2.343327742055726</v>
+        <v>23.43327742055726</v>
       </c>
       <c r="E122" t="n">
         <v>1256.64</v>
@@ -7401,10 +7401,10 @@
         <v>11.43548387096774</v>
       </c>
       <c r="N122" t="n">
-        <v>1.171663871027863</v>
+        <v>11.71663871027863</v>
       </c>
       <c r="O122" t="n">
-        <v>1.058441258444024</v>
+        <v>10.58441258444024</v>
       </c>
       <c r="P122" t="n">
         <v>0.9033659606790535</v>
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0.4115646258503401</v>
+        <v>4.115646258503402</v>
       </c>
       <c r="D123" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E123" t="n">
         <v>1861.688888888889</v>
@@ -7458,10 +7458,10 @@
         <v>13.5</v>
       </c>
       <c r="N123" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O123" t="n">
-        <v>1.145248198289217</v>
+        <v>11.45248198289217</v>
       </c>
       <c r="P123" t="n">
         <v>0.8954866231303982</v>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>4.683673469387755</v>
+        <v>46.83673469387755</v>
       </c>
       <c r="D124" t="n">
-        <v>2.358004845773926</v>
+        <v>23.58004845773926</v>
       </c>
       <c r="E124" t="n">
         <v>876.7255813953487</v>
@@ -7515,10 +7515,10 @@
         <v>13.46774193548384</v>
       </c>
       <c r="N124" t="n">
-        <v>1.179002422886963</v>
+        <v>11.79002422886963</v>
       </c>
       <c r="O124" t="n">
-        <v>1.045658443327717</v>
+        <v>10.45658443327717</v>
       </c>
       <c r="P124" t="n">
         <v>0.8869010131185877</v>
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>4.326530612244898</v>
+        <v>43.26530612244898</v>
       </c>
       <c r="D125" t="n">
-        <v>2.393439567607865</v>
+        <v>23.93439567607865</v>
       </c>
       <c r="E125" t="n">
         <v>1984.168421052631</v>
@@ -7572,10 +7572,10 @@
         <v>9.143548387096757</v>
       </c>
       <c r="N125" t="n">
-        <v>1.196719783803933</v>
+        <v>11.96719783803933</v>
       </c>
       <c r="O125" t="n">
-        <v>1.10618960175347</v>
+        <v>11.0618960175347</v>
       </c>
       <c r="P125" t="n">
         <v>0.9243513951422272</v>
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>4.506802721088436</v>
+        <v>45.06802721088435</v>
       </c>
       <c r="D126" t="n">
-        <v>2.376665734787065</v>
+        <v>23.76665734787066</v>
       </c>
       <c r="E126" t="n">
         <v>1396.266666666667</v>
@@ -7629,10 +7629,10 @@
         <v>11.54032258064518</v>
       </c>
       <c r="N126" t="n">
-        <v>1.188332867393533</v>
+        <v>11.88332867393533</v>
       </c>
       <c r="O126" t="n">
-        <v>1.074072247783184</v>
+        <v>10.74072247783184</v>
       </c>
       <c r="P126" t="n">
         <v>0.9038479682372452</v>
@@ -7653,10 +7653,10 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>4.295918367346939</v>
+        <v>42.95918367346939</v>
       </c>
       <c r="D127" t="n">
-        <v>2.402665175659304</v>
+        <v>24.02665175659304</v>
       </c>
       <c r="E127" t="n">
         <v>1346.4</v>
@@ -7686,10 +7686,10 @@
         <v>15.1241935483871</v>
       </c>
       <c r="N127" t="n">
-        <v>1.201332587829652</v>
+        <v>12.01332587829652</v>
       </c>
       <c r="O127" t="n">
-        <v>1.051588097251562</v>
+        <v>10.51588097251562</v>
       </c>
       <c r="P127" t="n">
         <v>0.8753513455848052</v>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2.63265306122449</v>
+        <v>26.3265306122449</v>
       </c>
       <c r="D128" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E128" t="n">
         <v>1848</v>
@@ -7743,10 +7743,10 @@
         <v>10.5</v>
       </c>
       <c r="N128" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O128" t="n">
-        <v>1.174951168586246</v>
+        <v>11.74951168586246</v>
       </c>
       <c r="P128" t="n">
         <v>0.9187118179903097</v>
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1.880952380952381</v>
+        <v>18.80952380952381</v>
       </c>
       <c r="D129" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E129" t="n">
         <v>1256.64</v>
@@ -7800,10 +7800,10 @@
         <v>23.5</v>
       </c>
       <c r="N129" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O129" t="n">
-        <v>1.046238297299118</v>
+        <v>10.46238297299118</v>
       </c>
       <c r="P129" t="n">
         <v>0.818069306930693</v>
@@ -7824,10 +7824,10 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4.48639455782313</v>
+        <v>44.8639455782313</v>
       </c>
       <c r="D130" t="n">
-        <v>2.395536296710465</v>
+        <v>23.95536296710464</v>
       </c>
       <c r="E130" t="n">
         <v>1358.52972972973</v>
@@ -7857,10 +7857,10 @@
         <v>10.2951612903226</v>
       </c>
       <c r="N130" t="n">
-        <v>1.197768148355232</v>
+        <v>11.97768148355232</v>
       </c>
       <c r="O130" t="n">
-        <v>1.095835858352038</v>
+        <v>10.95835858352038</v>
       </c>
       <c r="P130" t="n">
         <v>0.9148981460701165</v>
@@ -7881,10 +7881,10 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3.687074829931973</v>
+        <v>36.87074829931973</v>
       </c>
       <c r="D131" t="n">
-        <v>2.481711862827323</v>
+        <v>24.81711862827323</v>
       </c>
       <c r="E131" t="n">
         <v>1299.972413793103</v>
@@ -7914,10 +7914,10 @@
         <v>26.10806451612905</v>
       </c>
       <c r="N131" t="n">
-        <v>1.240855931413661</v>
+        <v>12.40855931413661</v>
       </c>
       <c r="O131" t="n">
-        <v>0.982360243135156</v>
+        <v>9.82360243135156</v>
       </c>
       <c r="P131" t="n">
         <v>0.7916795320597688</v>
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>8.802721088435373</v>
+        <v>88.02721088435374</v>
       </c>
       <c r="D132" t="n">
-        <v>1.854984109216654</v>
+        <v>18.54984109216655</v>
       </c>
       <c r="E132" t="n">
         <v>1396.266666666667</v>
@@ -7971,10 +7971,10 @@
         <v>8.082159624413151</v>
       </c>
       <c r="N132" t="n">
-        <v>0.9274920546083272</v>
+        <v>9.274920546083273</v>
       </c>
       <c r="O132" t="n">
-        <v>0.8474706721883951</v>
+        <v>8.474706721883951</v>
       </c>
       <c r="P132" t="n">
         <v>0.9137228378158726</v>
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>7.578231292517008</v>
+        <v>75.78231292517007</v>
       </c>
       <c r="D133" t="n">
-        <v>1.989066341521918</v>
+        <v>19.89066341521918</v>
       </c>
       <c r="E133" t="n">
         <v>2037.794594594594</v>
@@ -8028,10 +8028,10 @@
         <v>8.627543035993739</v>
       </c>
       <c r="N133" t="n">
-        <v>0.9945331707609588</v>
+        <v>9.945331707609588</v>
       </c>
       <c r="O133" t="n">
-        <v>0.909111952582803</v>
+        <v>9.091119525828029</v>
       </c>
       <c r="P133" t="n">
         <v>0.914109231658109</v>
@@ -8052,10 +8052,10 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>6.374149659863946</v>
+        <v>63.74149659863946</v>
       </c>
       <c r="D134" t="n">
-        <v>2.12490255651722</v>
+        <v>21.2490255651722</v>
       </c>
       <c r="E134" t="n">
         <v>1436.16</v>
@@ -8085,10 +8085,10 @@
         <v>8.464006259780916</v>
       </c>
       <c r="N134" t="n">
-        <v>1.06245127825861</v>
+        <v>10.6245127825861</v>
       </c>
       <c r="O134" t="n">
-        <v>0.9786492360825613</v>
+        <v>9.786492360825612</v>
       </c>
       <c r="P134" t="n">
         <v>0.9211238727921691</v>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>8.319727891156461</v>
+        <v>83.19727891156461</v>
       </c>
       <c r="D135" t="n">
-        <v>1.902536528813288</v>
+        <v>19.02536528813288</v>
       </c>
       <c r="E135" t="n">
         <v>2284.8</v>
@@ -8142,10 +8142,10 @@
         <v>17.3435054773083</v>
       </c>
       <c r="N135" t="n">
-        <v>0.9512682644066441</v>
+        <v>9.512682644066441</v>
       </c>
       <c r="O135" t="n">
-        <v>0.7795503883936907</v>
+        <v>7.795503883936908</v>
       </c>
       <c r="P135" t="n">
         <v>0.8194853308597834</v>
@@ -8166,10 +8166,10 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>6.612244897959184</v>
+        <v>66.12244897959184</v>
       </c>
       <c r="D136" t="n">
-        <v>2.116327530032581</v>
+        <v>21.16327530032581</v>
       </c>
       <c r="E136" t="n">
         <v>1142.4</v>
@@ -8199,10 +8199,10 @@
         <v>13.32394366197184</v>
       </c>
       <c r="N136" t="n">
-        <v>1.058163765016291</v>
+        <v>10.58163765016291</v>
       </c>
       <c r="O136" t="n">
-        <v>0.9262435307393416</v>
+        <v>9.262435307393416</v>
       </c>
       <c r="P136" t="n">
         <v>0.8753309850154262</v>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>7.197278911564626</v>
+        <v>71.97278911564626</v>
       </c>
       <c r="D137" t="n">
-        <v>2.031746586979552</v>
+        <v>20.31746586979552</v>
       </c>
       <c r="E137" t="n">
         <v>1256.64</v>
@@ -8256,10 +8256,10 @@
         <v>9.946791862284812</v>
       </c>
       <c r="N137" t="n">
-        <v>1.015873293489776</v>
+        <v>10.15873293489776</v>
       </c>
       <c r="O137" t="n">
-        <v>0.9173902057443817</v>
+        <v>9.173902057443817</v>
       </c>
       <c r="P137" t="n">
         <v>0.9030557369934586</v>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>8.826530612244897</v>
+        <v>88.26530612244896</v>
       </c>
       <c r="D138" t="n">
-        <v>1.846798856663135</v>
+        <v>18.46798856663135</v>
       </c>
       <c r="E138" t="n">
         <v>2432.206451612903</v>
@@ -8313,10 +8313,10 @@
         <v>7.087636932707369</v>
       </c>
       <c r="N138" t="n">
-        <v>0.9233994283315676</v>
+        <v>9.233994283315676</v>
       </c>
       <c r="O138" t="n">
-        <v>0.8532248052354551</v>
+        <v>8.53224805235455</v>
       </c>
       <c r="P138" t="n">
         <v>0.9240040431659065</v>
@@ -8337,10 +8337,10 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>8.428571428571427</v>
+        <v>84.28571428571428</v>
       </c>
       <c r="D139" t="n">
-        <v>1.883632493153971</v>
+        <v>18.83632493153971</v>
       </c>
       <c r="E139" t="n">
         <v>1256.64</v>
@@ -8370,10 +8370,10 @@
         <v>8.334115805946794</v>
       </c>
       <c r="N139" t="n">
-        <v>0.9418162465769854</v>
+        <v>9.418162465769853</v>
       </c>
       <c r="O139" t="n">
-        <v>0.8593002484983043</v>
+        <v>8.593002484983042</v>
       </c>
       <c r="P139" t="n">
         <v>0.9123863084985165</v>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>9.5578231292517</v>
+        <v>95.578231292517</v>
       </c>
       <c r="D140" t="n">
-        <v>1.766310539886865</v>
+        <v>17.66310539886866</v>
       </c>
       <c r="E140" t="n">
         <v>2185.460869565217</v>
@@ -8427,10 +8427,10 @@
         <v>9.3035993740219</v>
       </c>
       <c r="N140" t="n">
-        <v>0.8831552699434327</v>
+        <v>8.831552699434328</v>
       </c>
       <c r="O140" t="n">
-        <v>0.7910404246560873</v>
+        <v>7.910404246560873</v>
       </c>
       <c r="P140" t="n">
         <v>0.8956980177525912</v>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>6.472789115646258</v>
+        <v>64.72789115646259</v>
       </c>
       <c r="D141" t="n">
-        <v>2.116717303963701</v>
+        <v>21.16717303963701</v>
       </c>
       <c r="E141" t="n">
         <v>1256.64</v>
@@ -8484,10 +8484,10 @@
         <v>10.03677621283256</v>
       </c>
       <c r="N141" t="n">
-        <v>1.05835865198185</v>
+        <v>10.5835865198185</v>
       </c>
       <c r="O141" t="n">
-        <v>0.9589846300726171</v>
+        <v>9.589846300726171</v>
       </c>
       <c r="P141" t="n">
         <v>0.9061055326347561</v>
@@ -8508,10 +8508,10 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>8.272108843537413</v>
+        <v>82.72108843537413</v>
       </c>
       <c r="D142" t="n">
-        <v>1.905654720262248</v>
+        <v>19.05654720262248</v>
       </c>
       <c r="E142" t="n">
         <v>1733.296551724138</v>
@@ -8541,10 +8541,10 @@
         <v>8.255868544600929</v>
       </c>
       <c r="N142" t="n">
-        <v>0.9528273601311239</v>
+        <v>9.528273601311239</v>
       </c>
       <c r="O142" t="n">
-        <v>0.8710860874123029</v>
+        <v>8.710860874123028</v>
       </c>
       <c r="P142" t="n">
         <v>0.914211874953326</v>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>8.340136054421768</v>
+        <v>83.40136054421768</v>
       </c>
       <c r="D143" t="n">
-        <v>1.900392772192129</v>
+        <v>19.00392772192129</v>
       </c>
       <c r="E143" t="n">
         <v>1675.52</v>
@@ -8598,10 +8598,10 @@
         <v>7.528169014084511</v>
       </c>
       <c r="N143" t="n">
-        <v>0.9501963860960644</v>
+        <v>9.501963860960643</v>
       </c>
       <c r="O143" t="n">
-        <v>0.8756600592239405</v>
+        <v>8.756600592239405</v>
       </c>
       <c r="P143" t="n">
         <v>0.9215569244813059</v>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>8.85034013605442</v>
+        <v>88.5034013605442</v>
       </c>
       <c r="D144" t="n">
-        <v>1.846993743628695</v>
+        <v>18.46993743628695</v>
       </c>
       <c r="E144" t="n">
         <v>1713.6</v>
@@ -8655,10 +8655,10 @@
         <v>7.942097026604074</v>
       </c>
       <c r="N144" t="n">
-        <v>0.9234968718143476</v>
+        <v>9.234968718143476</v>
       </c>
       <c r="O144" t="n">
-        <v>0.8448622477885647</v>
+        <v>8.448622477885646</v>
       </c>
       <c r="P144" t="n">
         <v>0.914851228601031</v>
@@ -8679,10 +8679,10 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3.547619047619047</v>
+        <v>35.47619047619047</v>
       </c>
       <c r="D145" t="n">
-        <v>2.499114714378902</v>
+        <v>24.99114714378902</v>
       </c>
       <c r="E145" t="n">
         <v>1933.292307692308</v>
@@ -8712,10 +8712,10 @@
         <v>18.53709677419357</v>
       </c>
       <c r="N145" t="n">
-        <v>1.249557357189451</v>
+        <v>12.49557357189451</v>
       </c>
       <c r="O145" t="n">
-        <v>1.066021745563772</v>
+        <v>10.66021745563772</v>
       </c>
       <c r="P145" t="n">
         <v>0.853119498220959</v>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>4.751700680272108</v>
+        <v>47.51700680272108</v>
       </c>
       <c r="D146" t="n">
-        <v>2.347311527350666</v>
+        <v>23.47311527350666</v>
       </c>
       <c r="E146" t="n">
         <v>1178.1</v>
@@ -8769,10 +8769,10 @@
         <v>14.93709677419355</v>
       </c>
       <c r="N146" t="n">
-        <v>1.173655763675333</v>
+        <v>11.73655763675333</v>
       </c>
       <c r="O146" t="n">
-        <v>1.02576371640609</v>
+        <v>10.2576371640609</v>
       </c>
       <c r="P146" t="n">
         <v>0.8739902688279608</v>
@@ -8793,10 +8793,10 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1.969387755102041</v>
+        <v>19.69387755102041</v>
       </c>
       <c r="D147" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E147" t="n">
         <v>1299.972413793103</v>
@@ -8826,10 +8826,10 @@
         <v>26.5</v>
       </c>
       <c r="N147" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O147" t="n">
-        <v>1.016535327002088</v>
+        <v>10.16535327002088</v>
       </c>
       <c r="P147" t="n">
         <v>0.7948441120707815</v>
@@ -8850,10 +8850,10 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2.792517006802721</v>
+        <v>27.92517006802721</v>
       </c>
       <c r="D148" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E148" t="n">
         <v>1861.688888888889</v>
@@ -8883,10 +8883,10 @@
         <v>18.5</v>
       </c>
       <c r="N148" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O148" t="n">
-        <v>1.095743247794167</v>
+        <v>10.95743247794167</v>
       </c>
       <c r="P148" t="n">
         <v>0.8567779650305457</v>
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>4.333333333333333</v>
+        <v>43.33333333333333</v>
       </c>
       <c r="D149" t="n">
-        <v>2.413568166992824</v>
+        <v>24.13568166992824</v>
       </c>
       <c r="E149" t="n">
         <v>1795.2</v>
@@ -8940,10 +8940,10 @@
         <v>23.15483870967739</v>
       </c>
       <c r="N149" t="n">
-        <v>1.206784083496412</v>
+        <v>12.06784083496412</v>
       </c>
       <c r="O149" t="n">
-        <v>0.977528254687725</v>
+        <v>9.77528254687725</v>
       </c>
       <c r="P149" t="n">
         <v>0.8100274672628556</v>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3.540816326530612</v>
+        <v>35.40816326530612</v>
       </c>
       <c r="D150" t="n">
-        <v>2.496388966545522</v>
+        <v>24.96388966545522</v>
       </c>
       <c r="E150" t="n">
         <v>2416.615384615385</v>
@@ -8997,10 +8997,10 @@
         <v>7.312903225806451</v>
       </c>
       <c r="N150" t="n">
-        <v>1.248194483272761</v>
+        <v>12.48194483272761</v>
       </c>
       <c r="O150" t="n">
-        <v>1.175789500839034</v>
+        <v>11.75789500839034</v>
       </c>
       <c r="P150" t="n">
         <v>0.9419922268492313</v>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>6.551020408163265</v>
+        <v>65.51020408163265</v>
       </c>
       <c r="D151" t="n">
-        <v>2.114378660376981</v>
+        <v>21.14378660376981</v>
       </c>
       <c r="E151" t="n">
         <v>1570.8</v>
@@ -9054,10 +9054,10 @@
         <v>8.930359937402187</v>
       </c>
       <c r="N151" t="n">
-        <v>1.05718933018849</v>
+        <v>10.57189330188491</v>
       </c>
       <c r="O151" t="n">
-        <v>0.9687699248676769</v>
+        <v>9.687699248676768</v>
       </c>
       <c r="P151" t="n">
         <v>0.9163636987283544</v>
@@ -9078,10 +9078,10 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>8.319727891156461</v>
+        <v>83.19727891156461</v>
       </c>
       <c r="D152" t="n">
-        <v>1.898054128605409</v>
+        <v>18.98054128605409</v>
       </c>
       <c r="E152" t="n">
         <v>2393.6</v>
@@ -9111,10 +9111,10 @@
         <v>8.18309859154931</v>
       </c>
       <c r="N152" t="n">
-        <v>0.9490270643027044</v>
+        <v>9.490270643027044</v>
       </c>
       <c r="O152" t="n">
-        <v>0.8680062861685528</v>
+        <v>8.680062861685528</v>
       </c>
       <c r="P152" t="n">
         <v>0.9146275367882354</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>7.867346938775509</v>
+        <v>78.67346938775509</v>
       </c>
       <c r="D153" t="n">
-        <v>1.953791800755561</v>
+        <v>19.53791800755561</v>
       </c>
       <c r="E153" t="n">
         <v>1795.2</v>
@@ -9168,10 +9168,10 @@
         <v>8.81768388106417</v>
       </c>
       <c r="N153" t="n">
-        <v>0.9768959003777807</v>
+        <v>9.768959003777807</v>
       </c>
       <c r="O153" t="n">
-        <v>0.8895920995751652</v>
+        <v>8.895920995751652</v>
       </c>
       <c r="P153" t="n">
         <v>0.910631418589377</v>
@@ -9192,10 +9192,10 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>8.340136054421768</v>
+        <v>83.40136054421768</v>
       </c>
       <c r="D154" t="n">
-        <v>1.897079693777609</v>
+        <v>18.97079693777609</v>
       </c>
       <c r="E154" t="n">
         <v>1933.292307692308</v>
@@ -9225,10 +9225,10 @@
         <v>7.440532081377143</v>
       </c>
       <c r="N154" t="n">
-        <v>0.9485398468888044</v>
+        <v>9.485398468888045</v>
       </c>
       <c r="O154" t="n">
-        <v>0.8748712124197239</v>
+        <v>8.748712124197239</v>
       </c>
       <c r="P154" t="n">
         <v>0.9223346971550931</v>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>6.506802721088436</v>
+        <v>65.06802721088435</v>
       </c>
       <c r="D155" t="n">
-        <v>2.121394591137141</v>
+        <v>21.21394591137141</v>
       </c>
       <c r="E155" t="n">
         <v>1436.16</v>
@@ -9282,10 +9282,10 @@
         <v>10.08528951486699</v>
       </c>
       <c r="N155" t="n">
-        <v>1.060697295568571</v>
+        <v>10.60697295568571</v>
       </c>
       <c r="O155" t="n">
-        <v>0.960842943936224</v>
+        <v>9.60842943936224</v>
       </c>
       <c r="P155" t="n">
         <v>0.905859709410477</v>
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>10.03401360544218</v>
+        <v>100.3401360544218</v>
       </c>
       <c r="D156" t="n">
-        <v>1.723825181394791</v>
+        <v>17.23825181394791</v>
       </c>
       <c r="E156" t="n">
         <v>1507.968</v>
@@ -9339,10 +9339,10 @@
         <v>7.023474178403745</v>
       </c>
       <c r="N156" t="n">
-        <v>0.8619125906973956</v>
+        <v>8.619125906973956</v>
       </c>
       <c r="O156" t="n">
-        <v>0.7923732423963683</v>
+        <v>7.923732423963683</v>
       </c>
       <c r="P156" t="n">
         <v>0.9193197209884576</v>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>4.972789115646258</v>
+        <v>49.72789115646258</v>
       </c>
       <c r="D157" t="n">
-        <v>2.311038113875687</v>
+        <v>23.11038113875687</v>
       </c>
       <c r="E157" t="n">
         <v>1639.095652173913</v>
@@ -9396,10 +9396,10 @@
         <v>9.699999999999989</v>
       </c>
       <c r="N157" t="n">
-        <v>1.155519056937844</v>
+        <v>11.55519056937844</v>
       </c>
       <c r="O157" t="n">
-        <v>1.059479452977448</v>
+        <v>10.59479452977448</v>
       </c>
       <c r="P157" t="n">
         <v>0.9168861790865627</v>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>2.003401360544218</v>
+        <v>20.03401360544218</v>
       </c>
       <c r="D158" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E158" t="n">
         <v>1963.5</v>
@@ -9453,10 +9453,10 @@
         <v>10.5</v>
       </c>
       <c r="N158" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O158" t="n">
-        <v>1.174951168586246</v>
+        <v>11.74951168586246</v>
       </c>
       <c r="P158" t="n">
         <v>0.9187118179903097</v>
@@ -9477,10 +9477,10 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2.41156462585034</v>
+        <v>24.1156462585034</v>
       </c>
       <c r="D159" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E159" t="n">
         <v>1256.64</v>
@@ -9510,10 +9510,10 @@
         <v>10</v>
       </c>
       <c r="N159" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O159" t="n">
-        <v>1.179901663635751</v>
+        <v>11.79901663635751</v>
       </c>
       <c r="P159" t="n">
         <v>0.9225826838002948</v>
@@ -9534,10 +9534,10 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>2.571428571428572</v>
+        <v>25.71428571428572</v>
       </c>
       <c r="D160" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E160" t="n">
         <v>1675.52</v>
@@ -9567,10 +9567,10 @@
         <v>11</v>
       </c>
       <c r="N160" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O160" t="n">
-        <v>1.170000673536741</v>
+        <v>11.70000673536741</v>
       </c>
       <c r="P160" t="n">
         <v>0.9148409521803245</v>
@@ -9591,10 +9591,10 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>4.173469387755102</v>
+        <v>41.73469387755102</v>
       </c>
       <c r="D161" t="n">
-        <v>2.413777839903085</v>
+        <v>24.13777839903085</v>
       </c>
       <c r="E161" t="n">
         <v>2792.533333333333</v>
@@ -9624,10 +9624,10 @@
         <v>10.19516129032257</v>
       </c>
       <c r="N161" t="n">
-        <v>1.206888919951542</v>
+        <v>12.06888919951543</v>
       </c>
       <c r="O161" t="n">
-        <v>1.10594672895825</v>
+        <v>11.0594672895825</v>
       </c>
       <c r="P161" t="n">
         <v>0.9163616557211034</v>
@@ -9648,10 +9648,10 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>6.122448979591836</v>
+        <v>61.22448979591837</v>
       </c>
       <c r="D162" t="n">
-        <v>2.186702078091511</v>
+        <v>21.86702078091511</v>
       </c>
       <c r="E162" t="n">
         <v>2010.624</v>
@@ -9681,10 +9681,10 @@
         <v>15.74516129032259</v>
       </c>
       <c r="N162" t="n">
-        <v>1.093351039045755</v>
+        <v>10.93351039045755</v>
       </c>
       <c r="O162" t="n">
-        <v>0.9374583530029577</v>
+        <v>9.374583530029577</v>
       </c>
       <c r="P162" t="n">
         <v>0.8574175351963297</v>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>4.836734693877551</v>
+        <v>48.36734693877551</v>
       </c>
       <c r="D163" t="n">
-        <v>2.328021619606747</v>
+        <v>23.28021619606747</v>
       </c>
       <c r="E163" t="n">
         <v>1396.266666666667</v>
@@ -9738,10 +9738,10 @@
         <v>14.36451612903227</v>
       </c>
       <c r="N163" t="n">
-        <v>1.164010809803373</v>
+        <v>11.64010809803374</v>
       </c>
       <c r="O163" t="n">
-        <v>1.021787877832757</v>
+        <v>10.21787877832757</v>
       </c>
       <c r="P163" t="n">
         <v>0.8778164852312317</v>
@@ -9762,10 +9762,10 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>5.421768707482993</v>
+        <v>54.21768707482993</v>
       </c>
       <c r="D164" t="n">
-        <v>2.264071381977449</v>
+        <v>22.64071381977449</v>
       </c>
       <c r="E164" t="n">
         <v>1675.52</v>
@@ -9795,10 +9795,10 @@
         <v>8.033870967741933</v>
       </c>
       <c r="N164" t="n">
-        <v>1.132035690988724</v>
+        <v>11.32035690988724</v>
       </c>
       <c r="O164" t="n">
-        <v>1.052492414080388</v>
+        <v>10.52492414080388</v>
       </c>
       <c r="P164" t="n">
         <v>0.9297343029539443</v>
@@ -9819,10 +9819,10 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2.357142857142857</v>
+        <v>23.57142857142857</v>
       </c>
       <c r="D165" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E165" t="n">
         <v>1570.8</v>
@@ -9852,10 +9852,10 @@
         <v>12</v>
       </c>
       <c r="N165" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O165" t="n">
-        <v>1.160099683437732</v>
+        <v>11.60099683437732</v>
       </c>
       <c r="P165" t="n">
         <v>0.907099220560354</v>
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>2.520408163265306</v>
+        <v>25.20408163265306</v>
       </c>
       <c r="D166" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E166" t="n">
         <v>2094.4</v>
@@ -9909,10 +9909,10 @@
         <v>11.5</v>
       </c>
       <c r="N166" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O166" t="n">
-        <v>1.165050178487236</v>
+        <v>11.65050178487236</v>
       </c>
       <c r="P166" t="n">
         <v>0.9109700863703392</v>
@@ -9933,10 +9933,10 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4.078231292517007</v>
+        <v>40.78231292517007</v>
       </c>
       <c r="D167" t="n">
-        <v>2.430551672723884</v>
+        <v>24.30551672723884</v>
       </c>
       <c r="E167" t="n">
         <v>1507.968</v>
@@ -9966,10 +9966,10 @@
         <v>11.20645161290321</v>
       </c>
       <c r="N167" t="n">
-        <v>1.215275836361942</v>
+        <v>12.15275836361942</v>
       </c>
       <c r="O167" t="n">
-        <v>1.104320869897554</v>
+        <v>11.04320869897554</v>
       </c>
       <c r="P167" t="n">
         <v>0.9086997674564617</v>
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>5.22108843537415</v>
+        <v>52.2108843537415</v>
       </c>
       <c r="D168" t="n">
-        <v>2.297619047619047</v>
+        <v>22.97619047619047</v>
       </c>
       <c r="E168" t="n">
         <v>1346.4</v>
@@ -10023,10 +10023,10 @@
         <v>12.50483870967741</v>
       </c>
       <c r="N168" t="n">
-        <v>1.148809523809524</v>
+        <v>11.48809523809524</v>
       </c>
       <c r="O168" t="n">
-        <v>1.024999239555292</v>
+        <v>10.24999239555292</v>
       </c>
       <c r="P168" t="n">
         <v>0.8922273173331039</v>
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3.595238095238095</v>
+        <v>35.95238095238096</v>
       </c>
       <c r="D169" t="n">
-        <v>2.485485975212003</v>
+        <v>24.85485975212003</v>
       </c>
       <c r="E169" t="n">
         <v>1795.2</v>
@@ -10080,10 +10080,10 @@
         <v>8.24032258064517</v>
       </c>
       <c r="N169" t="n">
-        <v>1.242742987606001</v>
+        <v>12.42742987606001</v>
       </c>
       <c r="O169" t="n">
-        <v>1.161155635322386</v>
+        <v>11.61155635322386</v>
       </c>
       <c r="P169" t="n">
         <v>0.9343489739251847</v>
@@ -10104,10 +10104,10 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4.387755102040816</v>
+        <v>43.87755102040816</v>
       </c>
       <c r="D170" t="n">
-        <v>2.391762184325785</v>
+        <v>23.91762184325785</v>
       </c>
       <c r="E170" t="n">
         <v>1570.8</v>
@@ -10137,10 +10137,10 @@
         <v>9.245161290322585</v>
       </c>
       <c r="N170" t="n">
-        <v>1.195881092162893</v>
+        <v>11.95881092162893</v>
       </c>
       <c r="O170" t="n">
-        <v>1.104344841763659</v>
+        <v>11.04344841763659</v>
       </c>
       <c r="P170" t="n">
         <v>0.9234570635834041</v>
@@ -10161,10 +10161,10 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>3.581632653061225</v>
+        <v>35.81632653061224</v>
       </c>
       <c r="D171" t="n">
-        <v>2.488840741776162</v>
+        <v>24.88840741776162</v>
       </c>
       <c r="E171" t="n">
         <v>2185.460869565217</v>
@@ -10194,10 +10194,10 @@
         <v>7.251612903225805</v>
       </c>
       <c r="N171" t="n">
-        <v>1.244420370888081</v>
+        <v>12.44420370888081</v>
       </c>
       <c r="O171" t="n">
-        <v>1.17262222333139</v>
+        <v>11.7262222333139</v>
       </c>
       <c r="P171" t="n">
         <v>0.9423039438791473</v>
@@ -10218,10 +10218,10 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>4.809523809523809</v>
+        <v>48.09523809523809</v>
       </c>
       <c r="D172" t="n">
-        <v>2.347940546081446</v>
+        <v>23.47940546081446</v>
       </c>
       <c r="E172" t="n">
         <v>1256.64</v>
@@ -10251,10 +10251,10 @@
         <v>9.803225806451621</v>
       </c>
       <c r="N172" t="n">
-        <v>1.173970273040723</v>
+        <v>11.73970273040723</v>
       </c>
       <c r="O172" t="n">
-        <v>1.076908631392687</v>
+        <v>10.76908631392687</v>
       </c>
       <c r="P172" t="n">
         <v>0.9173218914678013</v>
@@ -10275,10 +10275,10 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>5.22108843537415</v>
+        <v>52.2108843537415</v>
       </c>
       <c r="D173" t="n">
-        <v>2.296361010157488</v>
+        <v>22.96361010157488</v>
       </c>
       <c r="E173" t="n">
         <v>1570.8</v>
@@ -10308,10 +10308,10 @@
         <v>12.06612903225806</v>
       </c>
       <c r="N173" t="n">
-        <v>1.148180505078744</v>
+        <v>11.48180505078744</v>
       </c>
       <c r="O173" t="n">
-        <v>1.028713880996981</v>
+        <v>10.28713880996981</v>
       </c>
       <c r="P173" t="n">
         <v>0.8959513564693647</v>
@@ -10332,10 +10332,10 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>4.071428571428571</v>
+        <v>40.71428571428571</v>
       </c>
       <c r="D174" t="n">
-        <v>2.436003168390644</v>
+        <v>24.36003168390643</v>
       </c>
       <c r="E174" t="n">
         <v>2513.28</v>
@@ -10365,10 +10365,10 @@
         <v>8.583870967741916</v>
       </c>
       <c r="N174" t="n">
-        <v>1.218001584195322</v>
+        <v>12.18001584195322</v>
       </c>
       <c r="O174" t="n">
-        <v>1.133012762732531</v>
+        <v>11.33012762732531</v>
       </c>
       <c r="P174" t="n">
         <v>0.9302227332331925</v>
@@ -10389,10 +10389,10 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>3.962585034013606</v>
+        <v>39.62585034013605</v>
       </c>
       <c r="D175" t="n">
-        <v>2.443341720249744</v>
+        <v>24.43341720249744</v>
       </c>
       <c r="E175" t="n">
         <v>1449.969230769231</v>
@@ -10422,10 +10422,10 @@
         <v>9.574193548387086</v>
       </c>
       <c r="N175" t="n">
-        <v>1.221670860124872</v>
+        <v>12.21670860124872</v>
       </c>
       <c r="O175" t="n">
-        <v>1.126876864596287</v>
+        <v>11.26876864596287</v>
       </c>
       <c r="P175" t="n">
         <v>0.9224062727346254</v>
@@ -10446,10 +10446,10 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>4.098639455782313</v>
+        <v>40.98639455782313</v>
       </c>
       <c r="D176" t="n">
-        <v>2.431180691454664</v>
+        <v>24.31180691454664</v>
       </c>
       <c r="E176" t="n">
         <v>1396.266666666667</v>
@@ -10479,10 +10479,10 @@
         <v>11.70645161290321</v>
       </c>
       <c r="N176" t="n">
-        <v>1.215590345727332</v>
+        <v>12.15590345727332</v>
       </c>
       <c r="O176" t="n">
-        <v>1.099684884213439</v>
+        <v>10.99684884213439</v>
       </c>
       <c r="P176" t="n">
         <v>0.9046508867717745</v>
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>3.938775510204082</v>
+        <v>39.38775510204082</v>
       </c>
       <c r="D177" t="n">
-        <v>2.449212561737023</v>
+        <v>24.49212561737023</v>
       </c>
       <c r="E177" t="n">
         <v>2393.6</v>
@@ -10536,10 +10536,10 @@
         <v>9.00322580645161</v>
       </c>
       <c r="N177" t="n">
-        <v>1.224606280868512</v>
+        <v>12.24606280868512</v>
       </c>
       <c r="O177" t="n">
-        <v>1.135465431299684</v>
+        <v>11.35465431299684</v>
       </c>
       <c r="P177" t="n">
         <v>0.9272085641226602</v>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>4.078231292517007</v>
+        <v>40.78231292517007</v>
       </c>
       <c r="D178" t="n">
-        <v>2.434116112198304</v>
+        <v>24.34116112198304</v>
       </c>
       <c r="E178" t="n">
         <v>2356.2</v>
@@ -10593,10 +10593,10 @@
         <v>9.991935483870975</v>
       </c>
       <c r="N178" t="n">
-        <v>1.217058056099152</v>
+        <v>12.17058056099152</v>
       </c>
       <c r="O178" t="n">
-        <v>1.1181280018034</v>
+        <v>11.181280018034</v>
       </c>
       <c r="P178" t="n">
         <v>0.9187137755672581</v>
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>6.166666666666667</v>
+        <v>61.66666666666667</v>
       </c>
       <c r="D179" t="n">
-        <v>2.169508899450192</v>
+        <v>21.69508899450192</v>
       </c>
       <c r="E179" t="n">
         <v>2284.8</v>
@@ -10650,10 +10650,10 @@
         <v>17.53064516129032</v>
       </c>
       <c r="N179" t="n">
-        <v>1.084754449725096</v>
+        <v>10.84754449725096</v>
       </c>
       <c r="O179" t="n">
-        <v>0.9111837055539043</v>
+        <v>9.111837055539043</v>
       </c>
       <c r="P179" t="n">
         <v>0.8399907516256987</v>
@@ -10674,10 +10674,10 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>6.782312925170069</v>
+        <v>67.82312925170069</v>
       </c>
       <c r="D180" t="n">
-        <v>2.080468328369546</v>
+        <v>20.80468328369545</v>
       </c>
       <c r="E180" t="n">
         <v>1358.52972972973</v>
@@ -10707,10 +10707,10 @@
         <v>10.62989045383412</v>
       </c>
       <c r="N180" t="n">
-        <v>1.040234164184773</v>
+        <v>10.40234164184773</v>
       </c>
       <c r="O180" t="n">
-        <v>0.9349877240478012</v>
+        <v>9.349877240478012</v>
       </c>
       <c r="P180" t="n">
         <v>0.8988242803778198</v>
@@ -10731,10 +10731,10 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>8.860544217687075</v>
+        <v>88.60544217687075</v>
       </c>
       <c r="D181" t="n">
-        <v>1.838613604109616</v>
+        <v>18.38613604109617</v>
       </c>
       <c r="E181" t="n">
         <v>1570.8</v>
@@ -10764,10 +10764,10 @@
         <v>9.820813771518004</v>
       </c>
       <c r="N181" t="n">
-        <v>0.9193068020548082</v>
+        <v>9.193068020548083</v>
       </c>
       <c r="O181" t="n">
-        <v>0.8220710221387884</v>
+        <v>8.220710221387883</v>
       </c>
       <c r="P181" t="n">
         <v>0.8942292391411863</v>
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>9.459183673469386</v>
+        <v>94.59183673469386</v>
       </c>
       <c r="D182" t="n">
-        <v>1.779367966579384</v>
+        <v>17.79367966579384</v>
       </c>
       <c r="E182" t="n">
         <v>1884.96</v>
@@ -10821,10 +10821,10 @@
         <v>8.079812206572768</v>
       </c>
       <c r="N182" t="n">
-        <v>0.8896839832896918</v>
+        <v>8.896839832896918</v>
       </c>
       <c r="O182" t="n">
-        <v>0.8096858426305554</v>
+        <v>8.096858426305554</v>
       </c>
       <c r="P182" t="n">
         <v>0.9100825212528436</v>
@@ -10845,10 +10845,10 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>8.42517006802721</v>
+        <v>84.25170068027211</v>
       </c>
       <c r="D183" t="n">
-        <v>1.883242719222851</v>
+        <v>18.83242719222851</v>
       </c>
       <c r="E183" t="n">
         <v>2393.6</v>
@@ -10878,10 +10878,10 @@
         <v>6.285602503912372</v>
       </c>
       <c r="N183" t="n">
-        <v>0.9416213596114253</v>
+        <v>9.416213596114254</v>
       </c>
       <c r="O183" t="n">
-        <v>0.879387671453877</v>
+        <v>8.79387671453877</v>
       </c>
       <c r="P183" t="n">
         <v>0.9339079476879858</v>
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>8.605442176870747</v>
+        <v>86.05442176870747</v>
       </c>
       <c r="D184" t="n">
-        <v>1.869600631633653</v>
+        <v>18.69600631633653</v>
       </c>
       <c r="E184" t="n">
         <v>2956.8</v>
@@ -10935,10 +10935,10 @@
         <v>8.436619718309856</v>
       </c>
       <c r="N184" t="n">
-        <v>0.9348003158168263</v>
+        <v>9.348003158168263</v>
       </c>
       <c r="O184" t="n">
-        <v>0.8512694275167288</v>
+        <v>8.512694275167288</v>
       </c>
       <c r="P184" t="n">
         <v>0.9106430679507115</v>
@@ -10959,10 +10959,10 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>8.836734693877549</v>
+        <v>88.36734693877548</v>
       </c>
       <c r="D185" t="n">
-        <v>1.845824421835336</v>
+        <v>18.45824421835336</v>
       </c>
       <c r="E185" t="n">
         <v>2645.557894736842</v>
@@ -10992,10 +10992,10 @@
         <v>7.514866979655721</v>
       </c>
       <c r="N185" t="n">
-        <v>0.9229122109176678</v>
+        <v>9.229122109176679</v>
       </c>
       <c r="O185" t="n">
-        <v>0.84850758735672</v>
+        <v>8.485075873567201</v>
       </c>
       <c r="P185" t="n">
         <v>0.9193806055648934</v>
@@ -11016,10 +11016,10 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>7.945578231292516</v>
+        <v>79.45578231292517</v>
       </c>
       <c r="D186" t="n">
-        <v>1.950673609306602</v>
+        <v>19.50673609306602</v>
       </c>
       <c r="E186" t="n">
         <v>1639.095652173913</v>
@@ -11049,10 +11049,10 @@
         <v>18.42957746478874</v>
       </c>
       <c r="N186" t="n">
-        <v>0.9753368046533012</v>
+        <v>9.753368046533012</v>
       </c>
       <c r="O186" t="n">
-        <v>0.7928657406454919</v>
+        <v>7.928657406454919</v>
       </c>
       <c r="P186" t="n">
         <v>0.8129148175919892</v>
@@ -11073,10 +11073,10 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>9.15986394557823</v>
+        <v>91.5986394557823</v>
       </c>
       <c r="D187" t="n">
-        <v>1.80918567231006</v>
+        <v>18.0918567231006</v>
       </c>
       <c r="E187" t="n">
         <v>2513.28</v>
@@ -11106,10 +11106,10 @@
         <v>6.438184663536788</v>
       </c>
       <c r="N187" t="n">
-        <v>0.9045928361550299</v>
+        <v>9.045928361550299</v>
       </c>
       <c r="O187" t="n">
-        <v>0.8408484335457548</v>
+        <v>8.408484335457548</v>
       </c>
       <c r="P187" t="n">
         <v>0.9295324923418357</v>
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>6.333333333333333</v>
+        <v>63.33333333333333</v>
       </c>
       <c r="D188" t="n">
-        <v>2.136206000519698</v>
+        <v>21.36206000519698</v>
       </c>
       <c r="E188" t="n">
         <v>1733.296551724138</v>
@@ -11163,10 +11163,10 @@
         <v>7.521909233176842</v>
       </c>
       <c r="N188" t="n">
-        <v>1.068103000259849</v>
+        <v>10.68103000259849</v>
       </c>
       <c r="O188" t="n">
-        <v>0.9936286514165141</v>
+        <v>9.936286514165142</v>
       </c>
       <c r="P188" t="n">
         <v>0.9302741881398922</v>
@@ -11187,10 +11187,10 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>7.340136054421769</v>
+        <v>73.40136054421768</v>
       </c>
       <c r="D189" t="n">
-        <v>2.015960742769193</v>
+        <v>20.15960742769193</v>
       </c>
       <c r="E189" t="n">
         <v>1795.2</v>
@@ -11220,10 +11220,10 @@
         <v>6.670579029733972</v>
       </c>
       <c r="N189" t="n">
-        <v>1.007980371384597</v>
+        <v>10.07980371384597</v>
       </c>
       <c r="O189" t="n">
-        <v>0.9419350344565377</v>
+        <v>9.419350344565377</v>
       </c>
       <c r="P189" t="n">
         <v>0.9344775565050568</v>
@@ -11244,10 +11244,10 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>7.585034013605441</v>
+        <v>75.85034013605441</v>
       </c>
       <c r="D190" t="n">
-        <v>1.986143037038518</v>
+        <v>19.86143037038518</v>
       </c>
       <c r="E190" t="n">
         <v>1795.2</v>
@@ -11277,10 +11277,10 @@
         <v>13.62754303599374</v>
       </c>
       <c r="N190" t="n">
-        <v>0.9930715185192588</v>
+        <v>9.930715185192588</v>
       </c>
       <c r="O190" t="n">
-        <v>0.8581453498460535</v>
+        <v>8.581453498460535</v>
       </c>
       <c r="P190" t="n">
         <v>0.8641324757008538</v>
@@ -11301,10 +11301,10 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>9.289115646258502</v>
+        <v>92.89115646258502</v>
       </c>
       <c r="D191" t="n">
-        <v>1.798661776169821</v>
+        <v>17.98661776169821</v>
       </c>
       <c r="E191" t="n">
         <v>2094.4</v>
@@ -11334,10 +11334,10 @@
         <v>6.807511737089214</v>
       </c>
       <c r="N191" t="n">
-        <v>0.8993308880849106</v>
+        <v>8.993308880849106</v>
       </c>
       <c r="O191" t="n">
-        <v>0.8319297817770966</v>
+        <v>8.319297817770966</v>
       </c>
       <c r="P191" t="n">
         <v>0.9250541628217153</v>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>3.299319727891156</v>
+        <v>32.99319727891157</v>
       </c>
       <c r="D192" t="n">
-        <v>2.523436771969062</v>
+        <v>25.23436771969062</v>
       </c>
       <c r="E192" t="n">
         <v>1984.168421052631</v>
@@ -11391,10 +11391,10 @@
         <v>8.079032258064501</v>
       </c>
       <c r="N192" t="n">
-        <v>1.261718385984531</v>
+        <v>12.61718385984531</v>
       </c>
       <c r="O192" t="n">
-        <v>1.181727967587853</v>
+        <v>11.81727967587853</v>
       </c>
       <c r="P192" t="n">
         <v>0.9366020030418587</v>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>4.843537414965986</v>
+        <v>48.43537414965986</v>
       </c>
       <c r="D193" t="n">
-        <v>2.330537694529867</v>
+        <v>23.30537694529867</v>
       </c>
       <c r="E193" t="n">
         <v>1795.2</v>
@@ -11448,10 +11448,10 @@
         <v>10.77419354838707</v>
       </c>
       <c r="N193" t="n">
-        <v>1.165268847264934</v>
+        <v>11.65268847264933</v>
       </c>
       <c r="O193" t="n">
-        <v>1.058593663617537</v>
+        <v>10.58593663617537</v>
       </c>
       <c r="P193" t="n">
         <v>0.9084544447422755</v>
@@ -11472,10 +11472,10 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2.602040816326531</v>
+        <v>26.02040816326531</v>
       </c>
       <c r="D194" t="n">
-        <v>2.557823129251701</v>
+        <v>25.57823129251701</v>
       </c>
       <c r="E194" t="n">
         <v>1861.688888888889</v>
@@ -11505,10 +11505,10 @@
         <v>8.5</v>
       </c>
       <c r="N194" t="n">
-        <v>1.27891156462585</v>
+        <v>12.78911564625851</v>
       </c>
       <c r="O194" t="n">
-        <v>1.194753148784266</v>
+        <v>11.94753148784266</v>
       </c>
       <c r="P194" t="n">
         <v>0.9341952812302506</v>
@@ -11529,10 +11529,10 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>4.299319727891157</v>
+        <v>42.99319727891157</v>
       </c>
       <c r="D195" t="n">
-        <v>2.409165035877365</v>
+        <v>24.09165035877365</v>
       </c>
       <c r="E195" t="n">
         <v>1713.6</v>
@@ -11562,10 +11562,10 @@
         <v>8.204838709677404</v>
       </c>
       <c r="N195" t="n">
-        <v>1.204582517938682</v>
+        <v>12.04582517938682</v>
       </c>
       <c r="O195" t="n">
-        <v>1.123346491110193</v>
+        <v>11.23346491110193</v>
       </c>
       <c r="P195" t="n">
         <v>0.9325608452565769</v>
@@ -11586,10 +11586,10 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>5.282312925170068</v>
+        <v>52.82312925170068</v>
       </c>
       <c r="D196" t="n">
-        <v>2.280845214798248</v>
+        <v>22.80845214798248</v>
       </c>
       <c r="E196" t="n">
         <v>1795.2</v>
@@ -11619,10 +11619,10 @@
         <v>10.92258064516128</v>
       </c>
       <c r="N196" t="n">
-        <v>1.140422607399124</v>
+        <v>11.40422607399124</v>
       </c>
       <c r="O196" t="n">
-        <v>1.032278244575745</v>
+        <v>10.32278244575745</v>
       </c>
       <c r="P196" t="n">
         <v>0.9051716774801443</v>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>3.146258503401361</v>
+        <v>31.46258503401361</v>
       </c>
       <c r="D197" t="n">
-        <v>2.536017146584661</v>
+        <v>25.36017146584661</v>
       </c>
       <c r="E197" t="n">
         <v>1449.969230769231</v>
@@ -11676,10 +11676,10 @@
         <v>5.75322580645161</v>
       </c>
       <c r="N197" t="n">
-        <v>1.26800857329233</v>
+        <v>12.6800857329233</v>
       </c>
       <c r="O197" t="n">
-        <v>1.211045941545285</v>
+        <v>12.11045941545285</v>
       </c>
       <c r="P197" t="n">
         <v>0.955077092579</v>
@@ -11700,10 +11700,10 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>3.789115646258503</v>
+        <v>37.89115646258503</v>
       </c>
       <c r="D198" t="n">
-        <v>2.464309011275743</v>
+        <v>24.64309011275743</v>
       </c>
       <c r="E198" t="n">
         <v>1639.095652173913</v>
@@ -11733,10 +11733,10 @@
         <v>10.16774193548389</v>
       </c>
       <c r="N198" t="n">
-        <v>1.232154505637871</v>
+        <v>12.32154505637871</v>
       </c>
       <c r="O198" t="n">
-        <v>1.131483793405358</v>
+        <v>11.31483793405358</v>
       </c>
       <c r="P198" t="n">
         <v>0.9182970059583576</v>
@@ -11757,10 +11757,10 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>5.244897959183674</v>
+        <v>52.44897959183674</v>
       </c>
       <c r="D199" t="n">
-        <v>2.283990308452148</v>
+        <v>22.83990308452148</v>
       </c>
       <c r="E199" t="n">
         <v>1396.266666666667</v>
@@ -11790,10 +11790,10 @@
         <v>11.50483870967741</v>
       </c>
       <c r="N199" t="n">
-        <v>1.141995154226074</v>
+        <v>11.41995154226074</v>
       </c>
       <c r="O199" t="n">
-        <v>1.028085860070852</v>
+        <v>10.28085860070852</v>
       </c>
       <c r="P199" t="n">
         <v>0.9002541352879752</v>
@@ -11814,10 +11814,10 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>5.710884353741497</v>
+        <v>57.10884353741497</v>
       </c>
       <c r="D200" t="n">
-        <v>2.23073338924611</v>
+        <v>22.3073338924611</v>
       </c>
       <c r="E200" t="n">
         <v>1861.688888888889</v>
@@ -11847,10 +11847,10 @@
         <v>8.879032258064512</v>
       </c>
       <c r="N200" t="n">
-        <v>1.115366694623055</v>
+        <v>11.15366694623055</v>
       </c>
       <c r="O200" t="n">
-        <v>1.027455484147169</v>
+        <v>10.27455484147169</v>
       </c>
       <c r="P200" t="n">
         <v>0.9211817863132479</v>
@@ -11871,10 +11871,10 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>9.146258503401359</v>
+        <v>91.46258503401359</v>
       </c>
       <c r="D201" t="n">
-        <v>1.81561694217354</v>
+        <v>18.1561694217354</v>
       </c>
       <c r="E201" t="n">
         <v>2645.557894736842</v>
@@ -11904,10 +11904,10 @@
         <v>6.48669796557121</v>
       </c>
       <c r="N201" t="n">
-        <v>0.9078084710867698</v>
+        <v>9.078084710867698</v>
       </c>
       <c r="O201" t="n">
-        <v>0.8435837387543814</v>
+        <v>8.435837387543813</v>
       </c>
       <c r="P201" t="n">
         <v>0.9292529929187568</v>
@@ -11928,10 +11928,10 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>6.710884353741496</v>
+        <v>67.10884353741496</v>
       </c>
       <c r="D202" t="n">
-        <v>2.078324571748386</v>
+        <v>20.78324571748386</v>
       </c>
       <c r="E202" t="n">
         <v>1523.2</v>
@@ -11961,10 +11961,10 @@
         <v>8.5813771517997</v>
       </c>
       <c r="N202" t="n">
-        <v>1.039162285874193</v>
+        <v>10.39162285874193</v>
       </c>
       <c r="O202" t="n">
-        <v>0.9541981556583544</v>
+        <v>9.541981556583544</v>
       </c>
       <c r="P202" t="n">
         <v>0.9182378620059688</v>
@@ -11985,10 +11985,10 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>9.095238095238095</v>
+        <v>90.95238095238095</v>
       </c>
       <c r="D203" t="n">
-        <v>1.819709568450299</v>
+        <v>18.19709568450299</v>
       </c>
       <c r="E203" t="n">
         <v>2284.8</v>
@@ -12018,10 +12018,10 @@
         <v>6.229264475743349</v>
       </c>
       <c r="N203" t="n">
-        <v>0.9098547842251495</v>
+        <v>9.098547842251495</v>
       </c>
       <c r="O203" t="n">
-        <v>0.8481788983267005</v>
+        <v>8.481788983267005</v>
       </c>
       <c r="P203" t="n">
         <v>0.9322134839891253</v>
@@ -12042,10 +12042,10 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>7.38095238095238</v>
+        <v>73.80952380952381</v>
       </c>
       <c r="D204" t="n">
-        <v>2.013622099182474</v>
+        <v>20.13622099182474</v>
       </c>
       <c r="E204" t="n">
         <v>1884.96</v>
@@ -12075,10 +12075,10 @@
         <v>9.267605633802816</v>
       </c>
       <c r="N204" t="n">
-        <v>1.006811049591237</v>
+        <v>10.06811049591237</v>
       </c>
       <c r="O204" t="n">
-        <v>0.9150525779694271</v>
+        <v>9.15052577969427</v>
       </c>
       <c r="P204" t="n">
         <v>0.9088622719634794</v>
@@ -12099,10 +12099,10 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>8.387755102040815</v>
+        <v>83.87755102040815</v>
       </c>
       <c r="D205" t="n">
-        <v>1.895910371984249</v>
+        <v>18.95910371984249</v>
       </c>
       <c r="E205" t="n">
         <v>2010.624</v>
@@ -12132,10 +12132,10 @@
         <v>6.819248826291073</v>
       </c>
       <c r="N205" t="n">
-        <v>0.9479551859921246</v>
+        <v>9.479551859921246</v>
       </c>
       <c r="O205" t="n">
-        <v>0.8804378708803318</v>
+        <v>8.804378708803318</v>
       </c>
       <c r="P205" t="n">
         <v>0.9287758365485077</v>
@@ -12156,10 +12156,10 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>9.15986394557823</v>
+        <v>91.5986394557823</v>
       </c>
       <c r="D206" t="n">
-        <v>1.806457254792221</v>
+        <v>18.06457254792221</v>
       </c>
       <c r="E206" t="n">
         <v>1639.095652173913</v>
@@ -12189,10 +12189,10 @@
         <v>7.36541471048514</v>
       </c>
       <c r="N206" t="n">
-        <v>0.9032286273961103</v>
+        <v>9.032286273961104</v>
       </c>
       <c r="O206" t="n">
-        <v>0.8303037292724951</v>
+        <v>8.303037292724952</v>
       </c>
       <c r="P206" t="n">
         <v>0.9192619720946532</v>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>8.646258503401359</v>
+        <v>86.46258503401359</v>
       </c>
       <c r="D207" t="n">
-        <v>1.870185292530333</v>
+        <v>18.70185292530333</v>
       </c>
       <c r="E207" t="n">
         <v>1713.6</v>
@@ -12246,10 +12246,10 @@
         <v>12.41236306729263</v>
       </c>
       <c r="N207" t="n">
-        <v>0.9350926462651663</v>
+        <v>9.350926462651664</v>
       </c>
       <c r="O207" t="n">
-        <v>0.8121979624305857</v>
+        <v>8.121979624305858</v>
       </c>
       <c r="P207" t="n">
         <v>0.8685748579828624</v>
@@ -12270,10 +12270,10 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>8.136054421768707</v>
+        <v>81.36054421768706</v>
       </c>
       <c r="D208" t="n">
-        <v>1.928651382198325</v>
+        <v>19.28651382198325</v>
       </c>
       <c r="E208" t="n">
         <v>1713.6</v>
@@ -12303,10 +12303,10 @@
         <v>19.17762128325509</v>
       </c>
       <c r="N208" t="n">
-        <v>0.9643256910991624</v>
+        <v>9.643256910991624</v>
       </c>
       <c r="O208" t="n">
-        <v>0.7744482526510922</v>
+        <v>7.744482526510922</v>
       </c>
       <c r="P208" t="n">
         <v>0.8030982268743218</v>
